--- a/Excel/LevelData.xlsx
+++ b/Excel/LevelData.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxcv2\OneDrive\문서\Addressable\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Color\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DB13E0-337B-4989-BA0C-C0D98C8A1859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6187BD3-427A-425A-888D-BCFCA5AD19E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LevelData" sheetId="7" r:id="rId1"/>
+    <sheet name="EnemyData" sheetId="8" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -35,7 +36,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>block_count</t>
+    <t>color_value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cube_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Color</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -74,7 +95,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -93,6 +114,48 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -106,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -115,6 +178,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -400,11 +470,1267 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{893968D5-95F3-4D8C-9E27-761EA7BEA57E}">
+  <dimension ref="A1:D103"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>0.95</v>
+      </c>
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>0.94</v>
+      </c>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>0.92</v>
+      </c>
+      <c r="D7" s="9"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>0.91</v>
+      </c>
+      <c r="D8" s="10"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>0.9</v>
+      </c>
+      <c r="D9" s="11"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>0.89</v>
+      </c>
+      <c r="D10" s="12"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>0.88</v>
+      </c>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>0.87</v>
+      </c>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>0.85</v>
+      </c>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>0.84</v>
+      </c>
+      <c r="D15" s="10"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>0.83</v>
+      </c>
+      <c r="D16" s="11"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>0.82</v>
+      </c>
+      <c r="D17" s="12"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>0.81</v>
+      </c>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3">
+        <v>6</v>
+      </c>
+      <c r="C19">
+        <v>0.8</v>
+      </c>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3">
+        <v>6</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" s="8"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3">
+        <v>6</v>
+      </c>
+      <c r="C21">
+        <v>0.78</v>
+      </c>
+      <c r="D21" s="9"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <v>0.77</v>
+      </c>
+      <c r="D22" s="10"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>0.76</v>
+      </c>
+      <c r="D23" s="11"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3">
+        <v>6</v>
+      </c>
+      <c r="C24">
+        <v>0.75</v>
+      </c>
+      <c r="D24" s="12"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3">
+        <v>6</v>
+      </c>
+      <c r="C25">
+        <v>0.74</v>
+      </c>
+      <c r="D25" s="6"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="4">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>0.73</v>
+      </c>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3">
+        <v>6</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="4">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3">
+        <v>6</v>
+      </c>
+      <c r="C28">
+        <v>0.71</v>
+      </c>
+      <c r="D28" s="9"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="4">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3">
+        <v>6</v>
+      </c>
+      <c r="C29">
+        <v>0.7</v>
+      </c>
+      <c r="D29" s="10"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="4">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3">
+        <v>6</v>
+      </c>
+      <c r="C30">
+        <v>0.69</v>
+      </c>
+      <c r="D30" s="11"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="4">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>0.68</v>
+      </c>
+      <c r="D31" s="12"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="4">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3">
+        <v>6</v>
+      </c>
+      <c r="C32">
+        <v>0.67</v>
+      </c>
+      <c r="D32" s="6"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3">
+        <v>6</v>
+      </c>
+      <c r="C33">
+        <v>0.66</v>
+      </c>
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="4">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3">
+        <v>6</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" s="8"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3">
+        <v>6</v>
+      </c>
+      <c r="C35">
+        <v>0.64</v>
+      </c>
+      <c r="D35" s="9"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="4">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3">
+        <v>6</v>
+      </c>
+      <c r="C36">
+        <v>0.63</v>
+      </c>
+      <c r="D36" s="10"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="4">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3">
+        <v>6</v>
+      </c>
+      <c r="C37">
+        <v>0.62</v>
+      </c>
+      <c r="D37" s="11"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="4">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>0.61</v>
+      </c>
+      <c r="D38" s="12"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3">
+        <v>6</v>
+      </c>
+      <c r="C39">
+        <v>0.6</v>
+      </c>
+      <c r="D39" s="6"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>0.59</v>
+      </c>
+      <c r="D40" s="7"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="4">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3">
+        <v>6</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" s="8"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="4">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3">
+        <v>6</v>
+      </c>
+      <c r="C42">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="D42" s="9"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="4">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3">
+        <v>6</v>
+      </c>
+      <c r="C43">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="D43" s="10"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="4">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3">
+        <v>6</v>
+      </c>
+      <c r="C44">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D44" s="11"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="4">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3">
+        <v>6</v>
+      </c>
+      <c r="C45">
+        <v>0.54</v>
+      </c>
+      <c r="D45" s="12"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="4">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3">
+        <v>6</v>
+      </c>
+      <c r="C46">
+        <v>0.53</v>
+      </c>
+      <c r="D46" s="6"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="4">
+        <v>44</v>
+      </c>
+      <c r="B47" s="3">
+        <v>6</v>
+      </c>
+      <c r="C47">
+        <v>0.52</v>
+      </c>
+      <c r="D47" s="7"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="4">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3">
+        <v>6</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" s="8"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="4">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3">
+        <v>6</v>
+      </c>
+      <c r="C49">
+        <v>0.5</v>
+      </c>
+      <c r="D49" s="9"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="4">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3">
+        <v>6</v>
+      </c>
+      <c r="C50">
+        <v>0.49</v>
+      </c>
+      <c r="D50" s="10"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="4">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3">
+        <v>6</v>
+      </c>
+      <c r="C51">
+        <v>0.48</v>
+      </c>
+      <c r="D51" s="11"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="4">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3">
+        <v>6</v>
+      </c>
+      <c r="C52">
+        <v>0.47</v>
+      </c>
+      <c r="D52" s="12"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="4">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3">
+        <v>6</v>
+      </c>
+      <c r="C53">
+        <v>0.46</v>
+      </c>
+      <c r="D53" s="6"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="4">
+        <v>51</v>
+      </c>
+      <c r="B54" s="3">
+        <v>6</v>
+      </c>
+      <c r="C54">
+        <v>0.45</v>
+      </c>
+      <c r="D54" s="7"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="4">
+        <v>52</v>
+      </c>
+      <c r="B55" s="3">
+        <v>6</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" s="8"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="4">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3">
+        <v>6</v>
+      </c>
+      <c r="C56">
+        <v>0.43</v>
+      </c>
+      <c r="D56" s="9"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="4">
+        <v>54</v>
+      </c>
+      <c r="B57" s="3">
+        <v>6</v>
+      </c>
+      <c r="C57">
+        <v>0.42</v>
+      </c>
+      <c r="D57" s="10"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="4">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3">
+        <v>6</v>
+      </c>
+      <c r="C58">
+        <v>0.41</v>
+      </c>
+      <c r="D58" s="11"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="4">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3">
+        <v>6</v>
+      </c>
+      <c r="C59">
+        <v>0.4</v>
+      </c>
+      <c r="D59" s="12"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="4">
+        <v>57</v>
+      </c>
+      <c r="B60" s="3">
+        <v>6</v>
+      </c>
+      <c r="C60">
+        <v>0.39</v>
+      </c>
+      <c r="D60" s="6"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="4">
+        <v>58</v>
+      </c>
+      <c r="B61" s="3">
+        <v>6</v>
+      </c>
+      <c r="C61">
+        <v>0.37999999999999901</v>
+      </c>
+      <c r="D61" s="7"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="4">
+        <v>59</v>
+      </c>
+      <c r="B62" s="3">
+        <v>6</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" s="8"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="4">
+        <v>60</v>
+      </c>
+      <c r="B63" s="3">
+        <v>6</v>
+      </c>
+      <c r="C63">
+        <v>0.35999999999999899</v>
+      </c>
+      <c r="D63" s="9"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="4">
+        <v>61</v>
+      </c>
+      <c r="B64" s="3">
+        <v>6</v>
+      </c>
+      <c r="C64">
+        <v>0.34999999999999898</v>
+      </c>
+      <c r="D64" s="10"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="4">
+        <v>62</v>
+      </c>
+      <c r="B65" s="3">
+        <v>6</v>
+      </c>
+      <c r="C65">
+        <v>0.33999999999999903</v>
+      </c>
+      <c r="D65" s="11"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="4">
+        <v>63</v>
+      </c>
+      <c r="B66" s="3">
+        <v>6</v>
+      </c>
+      <c r="C66">
+        <v>0.32999999999999902</v>
+      </c>
+      <c r="D66" s="12"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="4">
+        <v>64</v>
+      </c>
+      <c r="B67" s="3">
+        <v>6</v>
+      </c>
+      <c r="C67">
+        <v>0.31999999999999901</v>
+      </c>
+      <c r="D67" s="6"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="4">
+        <v>65</v>
+      </c>
+      <c r="B68" s="3">
+        <v>6</v>
+      </c>
+      <c r="C68">
+        <v>0.309999999999999</v>
+      </c>
+      <c r="D68" s="7"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="4">
+        <v>66</v>
+      </c>
+      <c r="B69" s="3">
+        <v>6</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69" s="8"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="4">
+        <v>67</v>
+      </c>
+      <c r="B70" s="3">
+        <v>6</v>
+      </c>
+      <c r="C70">
+        <v>0.28999999999999898</v>
+      </c>
+      <c r="D70" s="9"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="4">
+        <v>68</v>
+      </c>
+      <c r="B71" s="3">
+        <v>6</v>
+      </c>
+      <c r="C71">
+        <v>0.27999999999999903</v>
+      </c>
+      <c r="D71" s="10"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="4">
+        <v>69</v>
+      </c>
+      <c r="B72" s="3">
+        <v>6</v>
+      </c>
+      <c r="C72">
+        <v>0.26999999999999902</v>
+      </c>
+      <c r="D72" s="11"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="4">
+        <v>70</v>
+      </c>
+      <c r="B73" s="3">
+        <v>6</v>
+      </c>
+      <c r="C73">
+        <v>0.25999999999999901</v>
+      </c>
+      <c r="D73" s="12"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="4">
+        <v>71</v>
+      </c>
+      <c r="B74" s="3">
+        <v>6</v>
+      </c>
+      <c r="C74">
+        <v>0.249999999999999</v>
+      </c>
+      <c r="D74" s="6"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="4">
+        <v>72</v>
+      </c>
+      <c r="B75" s="3">
+        <v>6</v>
+      </c>
+      <c r="C75">
+        <v>0.23999999999999899</v>
+      </c>
+      <c r="D75" s="7"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="4">
+        <v>73</v>
+      </c>
+      <c r="B76" s="3">
+        <v>6</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76" s="8"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="4">
+        <v>74</v>
+      </c>
+      <c r="B77" s="3">
+        <v>6</v>
+      </c>
+      <c r="C77">
+        <v>0.219999999999999</v>
+      </c>
+      <c r="D77" s="9"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="4">
+        <v>75</v>
+      </c>
+      <c r="B78" s="3">
+        <v>6</v>
+      </c>
+      <c r="C78">
+        <v>0.20999999999999899</v>
+      </c>
+      <c r="D78" s="10"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="4">
+        <v>76</v>
+      </c>
+      <c r="B79" s="3">
+        <v>6</v>
+      </c>
+      <c r="C79">
+        <v>0.19999999999999901</v>
+      </c>
+      <c r="D79" s="11"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="4">
+        <v>77</v>
+      </c>
+      <c r="B80" s="3">
+        <v>6</v>
+      </c>
+      <c r="C80">
+        <v>0.189999999999999</v>
+      </c>
+      <c r="D80" s="12"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="4">
+        <v>78</v>
+      </c>
+      <c r="B81" s="3">
+        <v>6</v>
+      </c>
+      <c r="C81">
+        <v>0.17999999999999899</v>
+      </c>
+      <c r="D81" s="6"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="4">
+        <v>79</v>
+      </c>
+      <c r="B82" s="3">
+        <v>6</v>
+      </c>
+      <c r="C82">
+        <v>0.16999999999999901</v>
+      </c>
+      <c r="D82" s="7"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="4">
+        <v>80</v>
+      </c>
+      <c r="B83" s="3">
+        <v>6</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83" s="8"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="4">
+        <v>81</v>
+      </c>
+      <c r="B84" s="3">
+        <v>6</v>
+      </c>
+      <c r="C84">
+        <v>0.149999999999999</v>
+      </c>
+      <c r="D84" s="9"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="4">
+        <v>82</v>
+      </c>
+      <c r="B85" s="3">
+        <v>6</v>
+      </c>
+      <c r="C85">
+        <v>0.13999999999999899</v>
+      </c>
+      <c r="D85" s="10"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="4">
+        <v>83</v>
+      </c>
+      <c r="B86" s="3">
+        <v>6</v>
+      </c>
+      <c r="C86">
+        <v>0.12999999999999901</v>
+      </c>
+      <c r="D86" s="11"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="4">
+        <v>84</v>
+      </c>
+      <c r="B87" s="3">
+        <v>6</v>
+      </c>
+      <c r="C87">
+        <v>0.119999999999999</v>
+      </c>
+      <c r="D87" s="12"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="4">
+        <v>85</v>
+      </c>
+      <c r="B88" s="3">
+        <v>6</v>
+      </c>
+      <c r="C88">
+        <v>0.109999999999999</v>
+      </c>
+      <c r="D88" s="6"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="4">
+        <v>86</v>
+      </c>
+      <c r="B89" s="3">
+        <v>6</v>
+      </c>
+      <c r="C89">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D89" s="7"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="4">
+        <v>87</v>
+      </c>
+      <c r="B90" s="3">
+        <v>6</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="D90" s="8"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="4">
+        <v>88</v>
+      </c>
+      <c r="B91" s="3">
+        <v>6</v>
+      </c>
+      <c r="C91">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D91" s="9"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="4">
+        <v>89</v>
+      </c>
+      <c r="B92" s="3">
+        <v>6</v>
+      </c>
+      <c r="C92">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D92" s="10"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="4">
+        <v>90</v>
+      </c>
+      <c r="B93" s="3">
+        <v>6</v>
+      </c>
+      <c r="C93">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D93" s="11"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="4">
+        <v>91</v>
+      </c>
+      <c r="B94" s="3">
+        <v>6</v>
+      </c>
+      <c r="C94">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D94" s="12"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="4">
+        <v>92</v>
+      </c>
+      <c r="B95" s="3">
+        <v>6</v>
+      </c>
+      <c r="C95">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D95" s="6"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="4">
+        <v>93</v>
+      </c>
+      <c r="B96" s="3">
+        <v>6</v>
+      </c>
+      <c r="C96">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D96" s="7"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="4">
+        <v>94</v>
+      </c>
+      <c r="B97" s="3">
+        <v>6</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97" s="8"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="4">
+        <v>95</v>
+      </c>
+      <c r="B98" s="3">
+        <v>6</v>
+      </c>
+      <c r="C98">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D98" s="9"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="4">
+        <v>96</v>
+      </c>
+      <c r="B99" s="3">
+        <v>6</v>
+      </c>
+      <c r="C99">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D99" s="10"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="4">
+        <v>97</v>
+      </c>
+      <c r="B100" s="3">
+        <v>6</v>
+      </c>
+      <c r="C100">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D100" s="11"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="4">
+        <v>98</v>
+      </c>
+      <c r="B101" s="3">
+        <v>6</v>
+      </c>
+      <c r="C101">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D101" s="12"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="4">
+        <v>99</v>
+      </c>
+      <c r="B102" s="3">
+        <v>6</v>
+      </c>
+      <c r="C102">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D102" s="6"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="4">
+        <v>100</v>
+      </c>
+      <c r="B103" s="3">
+        <v>6</v>
+      </c>
+      <c r="C103">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D103" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FBBFF61-F2A9-4270-86EF-F5F8D76F72F6}">
   <dimension ref="A1:B103"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.125" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -412,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -427,813 +1753,812 @@
       <c r="A3" s="4">
         <v>0</v>
       </c>
-      <c r="B3" s="3">
-        <v>6</v>
+      <c r="B3" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="3">
-        <v>6</v>
+      <c r="B4" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="B5" s="3">
-        <v>6</v>
+      <c r="B5" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="3">
-        <v>6</v>
+      <c r="B6" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="3">
-        <v>6</v>
+      <c r="B7" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="B8" s="3">
-        <v>6</v>
+      <c r="B8" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>6</v>
       </c>
-      <c r="B9" s="3">
-        <v>6</v>
+      <c r="B9" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>7</v>
       </c>
-      <c r="B10" s="3">
-        <v>6</v>
+      <c r="B10" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>8</v>
       </c>
-      <c r="B11" s="3">
-        <v>6</v>
+      <c r="B11" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>9</v>
       </c>
-      <c r="B12" s="3">
-        <v>6</v>
+      <c r="B12" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>10</v>
       </c>
-      <c r="B13" s="3">
-        <v>6</v>
+      <c r="B13" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>11</v>
       </c>
-      <c r="B14" s="3">
-        <v>6</v>
+      <c r="B14" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>12</v>
       </c>
-      <c r="B15" s="3">
-        <v>6</v>
+      <c r="B15" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>13</v>
       </c>
-      <c r="B16" s="3">
-        <v>6</v>
+      <c r="B16" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>14</v>
       </c>
-      <c r="B17" s="3">
-        <v>6</v>
+      <c r="B17" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>15</v>
       </c>
-      <c r="B18" s="3">
-        <v>6</v>
+      <c r="B18" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>16</v>
       </c>
-      <c r="B19" s="3">
-        <v>6</v>
+      <c r="B19" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>17</v>
       </c>
-      <c r="B20" s="3">
-        <v>6</v>
+      <c r="B20" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>18</v>
       </c>
-      <c r="B21" s="3">
-        <v>6</v>
+      <c r="B21" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>19</v>
       </c>
-      <c r="B22" s="3">
-        <v>6</v>
+      <c r="B22" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>20</v>
       </c>
-      <c r="B23" s="3">
-        <v>6</v>
+      <c r="B23" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>21</v>
       </c>
-      <c r="B24" s="3">
-        <v>6</v>
+      <c r="B24" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>22</v>
       </c>
-      <c r="B25" s="3">
-        <v>6</v>
+      <c r="B25" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>23</v>
       </c>
-      <c r="B26" s="3">
-        <v>6</v>
+      <c r="B26" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>24</v>
       </c>
-      <c r="B27" s="3">
-        <v>6</v>
+      <c r="B27" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>25</v>
       </c>
-      <c r="B28" s="3">
-        <v>6</v>
+      <c r="B28" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>26</v>
       </c>
-      <c r="B29" s="3">
-        <v>6</v>
+      <c r="B29" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>27</v>
       </c>
-      <c r="B30" s="3">
-        <v>6</v>
+      <c r="B30" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>28</v>
       </c>
-      <c r="B31" s="3">
-        <v>6</v>
+      <c r="B31" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>29</v>
       </c>
-      <c r="B32" s="3">
-        <v>6</v>
+      <c r="B32" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>30</v>
       </c>
-      <c r="B33" s="3">
-        <v>6</v>
+      <c r="B33" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>31</v>
       </c>
-      <c r="B34" s="3">
-        <v>6</v>
+      <c r="B34" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>32</v>
       </c>
-      <c r="B35" s="3">
-        <v>6</v>
+      <c r="B35" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>33</v>
       </c>
-      <c r="B36" s="3">
-        <v>6</v>
+      <c r="B36" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>34</v>
       </c>
-      <c r="B37" s="3">
-        <v>6</v>
+      <c r="B37" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>35</v>
       </c>
-      <c r="B38" s="3">
-        <v>6</v>
+      <c r="B38" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>36</v>
       </c>
-      <c r="B39" s="3">
-        <v>6</v>
+      <c r="B39" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>37</v>
       </c>
-      <c r="B40" s="3">
-        <v>6</v>
+      <c r="B40" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>38</v>
       </c>
-      <c r="B41" s="3">
-        <v>6</v>
+      <c r="B41" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>39</v>
       </c>
-      <c r="B42" s="3">
-        <v>6</v>
+      <c r="B42" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>40</v>
       </c>
-      <c r="B43" s="3">
-        <v>6</v>
+      <c r="B43" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>41</v>
       </c>
-      <c r="B44" s="3">
-        <v>6</v>
+      <c r="B44" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>42</v>
       </c>
-      <c r="B45" s="3">
-        <v>6</v>
+      <c r="B45" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>43</v>
       </c>
-      <c r="B46" s="3">
-        <v>6</v>
+      <c r="B46" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>44</v>
       </c>
-      <c r="B47" s="3">
-        <v>6</v>
+      <c r="B47" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>45</v>
       </c>
-      <c r="B48" s="3">
-        <v>6</v>
+      <c r="B48" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>46</v>
       </c>
-      <c r="B49" s="3">
-        <v>6</v>
+      <c r="B49" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>47</v>
       </c>
-      <c r="B50" s="3">
-        <v>6</v>
+      <c r="B50" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>48</v>
       </c>
-      <c r="B51" s="3">
-        <v>6</v>
+      <c r="B51" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>49</v>
       </c>
-      <c r="B52" s="3">
-        <v>6</v>
+      <c r="B52" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>50</v>
       </c>
-      <c r="B53" s="3">
-        <v>6</v>
+      <c r="B53" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>51</v>
       </c>
-      <c r="B54" s="3">
-        <v>6</v>
+      <c r="B54" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>52</v>
       </c>
-      <c r="B55" s="3">
-        <v>6</v>
+      <c r="B55" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>53</v>
       </c>
-      <c r="B56" s="3">
-        <v>6</v>
+      <c r="B56" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>54</v>
       </c>
-      <c r="B57" s="3">
-        <v>6</v>
+      <c r="B57" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>55</v>
       </c>
-      <c r="B58" s="3">
-        <v>6</v>
+      <c r="B58" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>56</v>
       </c>
-      <c r="B59" s="3">
-        <v>6</v>
+      <c r="B59" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>57</v>
       </c>
-      <c r="B60" s="3">
-        <v>6</v>
+      <c r="B60" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>58</v>
       </c>
-      <c r="B61" s="3">
-        <v>6</v>
+      <c r="B61" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>59</v>
       </c>
-      <c r="B62" s="3">
-        <v>6</v>
+      <c r="B62" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>60</v>
       </c>
-      <c r="B63" s="3">
-        <v>6</v>
+      <c r="B63" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>61</v>
       </c>
-      <c r="B64" s="3">
-        <v>6</v>
+      <c r="B64" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>62</v>
       </c>
-      <c r="B65" s="3">
-        <v>6</v>
+      <c r="B65" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>63</v>
       </c>
-      <c r="B66" s="3">
-        <v>6</v>
+      <c r="B66" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>64</v>
       </c>
-      <c r="B67" s="3">
-        <v>6</v>
+      <c r="B67" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>65</v>
       </c>
-      <c r="B68" s="3">
-        <v>6</v>
+      <c r="B68" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>66</v>
       </c>
-      <c r="B69" s="3">
-        <v>6</v>
+      <c r="B69" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>67</v>
       </c>
-      <c r="B70" s="3">
-        <v>6</v>
+      <c r="B70" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>68</v>
       </c>
-      <c r="B71" s="3">
-        <v>6</v>
+      <c r="B71" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>69</v>
       </c>
-      <c r="B72" s="3">
-        <v>6</v>
+      <c r="B72" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>70</v>
       </c>
-      <c r="B73" s="3">
-        <v>6</v>
+      <c r="B73" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>71</v>
       </c>
-      <c r="B74" s="3">
-        <v>6</v>
+      <c r="B74" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>72</v>
       </c>
-      <c r="B75" s="3">
-        <v>6</v>
+      <c r="B75" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>73</v>
       </c>
-      <c r="B76" s="3">
-        <v>6</v>
+      <c r="B76" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>74</v>
       </c>
-      <c r="B77" s="3">
-        <v>6</v>
+      <c r="B77" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>75</v>
       </c>
-      <c r="B78" s="3">
-        <v>6</v>
+      <c r="B78" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>76</v>
       </c>
-      <c r="B79" s="3">
-        <v>6</v>
+      <c r="B79" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>77</v>
       </c>
-      <c r="B80" s="3">
-        <v>6</v>
+      <c r="B80" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>78</v>
       </c>
-      <c r="B81" s="3">
-        <v>6</v>
+      <c r="B81" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>79</v>
       </c>
-      <c r="B82" s="3">
-        <v>6</v>
+      <c r="B82" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>80</v>
       </c>
-      <c r="B83" s="3">
-        <v>6</v>
+      <c r="B83" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>81</v>
       </c>
-      <c r="B84" s="3">
-        <v>6</v>
+      <c r="B84" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>82</v>
       </c>
-      <c r="B85" s="3">
-        <v>6</v>
+      <c r="B85" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>83</v>
       </c>
-      <c r="B86" s="3">
-        <v>6</v>
+      <c r="B86" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>84</v>
       </c>
-      <c r="B87" s="3">
-        <v>6</v>
+      <c r="B87" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>85</v>
       </c>
-      <c r="B88" s="3">
-        <v>6</v>
+      <c r="B88" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>86</v>
       </c>
-      <c r="B89" s="3">
-        <v>6</v>
+      <c r="B89" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>87</v>
       </c>
-      <c r="B90" s="3">
-        <v>6</v>
+      <c r="B90" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>88</v>
       </c>
-      <c r="B91" s="3">
-        <v>6</v>
+      <c r="B91" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>89</v>
       </c>
-      <c r="B92" s="3">
-        <v>6</v>
+      <c r="B92" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>90</v>
       </c>
-      <c r="B93" s="3">
-        <v>6</v>
+      <c r="B93" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>91</v>
       </c>
-      <c r="B94" s="3">
-        <v>6</v>
+      <c r="B94" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>92</v>
       </c>
-      <c r="B95" s="3">
-        <v>6</v>
+      <c r="B95" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>93</v>
       </c>
-      <c r="B96" s="3">
-        <v>6</v>
+      <c r="B96" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>94</v>
       </c>
-      <c r="B97" s="3">
-        <v>6</v>
+      <c r="B97" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>95</v>
       </c>
-      <c r="B98" s="3">
-        <v>6</v>
+      <c r="B98" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>96</v>
       </c>
-      <c r="B99" s="3">
-        <v>6</v>
+      <c r="B99" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>97</v>
       </c>
-      <c r="B100" s="3">
-        <v>6</v>
+      <c r="B100" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>98</v>
       </c>
-      <c r="B101" s="3">
-        <v>6</v>
+      <c r="B101" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>99</v>
       </c>
-      <c r="B102" s="3">
-        <v>6</v>
+      <c r="B102" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>100</v>
       </c>
-      <c r="B103" s="3">
-        <v>6</v>
+      <c r="B103" s="5">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/LevelData.xlsx
+++ b/Excel/LevelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Color\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6187BD3-427A-425A-888D-BCFCA5AD19E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FCD307-E951-4872-9E88-D21233BD6414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="3405" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LevelData" sheetId="7" r:id="rId1"/>

--- a/Excel/LevelData.xlsx
+++ b/Excel/LevelData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Color\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FCD307-E951-4872-9E88-D21233BD6414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0412A7FD-56D3-4162-A754-F980D6C59E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3405" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1746,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -1762,7 +1762,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -1770,7 +1770,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -1778,7 +1778,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1786,7 +1786,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -1794,7 +1794,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -1802,7 +1802,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -1810,7 +1810,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1818,7 +1818,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -1826,7 +1826,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -1834,7 +1834,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -1842,7 +1842,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -1850,7 +1850,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -1858,7 +1858,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -1866,7 +1866,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -1874,7 +1874,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -1882,7 +1882,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -1890,7 +1890,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -1898,7 +1898,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -1906,7 +1906,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -1914,7 +1914,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -1922,7 +1922,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -1930,7 +1930,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -1938,7 +1938,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -1946,7 +1946,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -1954,7 +1954,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -1962,7 +1962,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -1970,7 +1970,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -1978,7 +1978,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -1986,7 +1986,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -1994,7 +1994,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -2002,7 +2002,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -2010,7 +2010,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -2018,7 +2018,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -2026,7 +2026,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -2034,7 +2034,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -2042,7 +2042,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -2050,7 +2050,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -2058,7 +2058,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -2066,7 +2066,7 @@
         <v>39</v>
       </c>
       <c r="B42" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -2074,7 +2074,7 @@
         <v>40</v>
       </c>
       <c r="B43" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -2082,7 +2082,7 @@
         <v>41</v>
       </c>
       <c r="B44" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -2090,7 +2090,7 @@
         <v>42</v>
       </c>
       <c r="B45" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -2098,7 +2098,7 @@
         <v>43</v>
       </c>
       <c r="B46" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
@@ -2106,7 +2106,7 @@
         <v>44</v>
       </c>
       <c r="B47" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -2114,7 +2114,7 @@
         <v>45</v>
       </c>
       <c r="B48" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -2122,7 +2122,7 @@
         <v>46</v>
       </c>
       <c r="B49" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -2130,7 +2130,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -2138,7 +2138,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -2146,7 +2146,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -2154,7 +2154,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -2162,7 +2162,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -2170,7 +2170,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -2178,7 +2178,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -2186,7 +2186,7 @@
         <v>54</v>
       </c>
       <c r="B57" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -2194,7 +2194,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -2202,7 +2202,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -2210,7 +2210,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -2218,7 +2218,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -2226,7 +2226,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -2234,7 +2234,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -2242,7 +2242,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -2250,7 +2250,7 @@
         <v>62</v>
       </c>
       <c r="B65" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -2258,7 +2258,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -2266,7 +2266,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -2274,7 +2274,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
@@ -2282,7 +2282,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
@@ -2290,7 +2290,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
@@ -2298,7 +2298,7 @@
         <v>68</v>
       </c>
       <c r="B71" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
@@ -2306,7 +2306,7 @@
         <v>69</v>
       </c>
       <c r="B72" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -2314,7 +2314,7 @@
         <v>70</v>
       </c>
       <c r="B73" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
@@ -2322,7 +2322,7 @@
         <v>71</v>
       </c>
       <c r="B74" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
@@ -2330,7 +2330,7 @@
         <v>72</v>
       </c>
       <c r="B75" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -2338,7 +2338,7 @@
         <v>73</v>
       </c>
       <c r="B76" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -2346,7 +2346,7 @@
         <v>74</v>
       </c>
       <c r="B77" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -2354,7 +2354,7 @@
         <v>75</v>
       </c>
       <c r="B78" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -2362,7 +2362,7 @@
         <v>76</v>
       </c>
       <c r="B79" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
@@ -2370,7 +2370,7 @@
         <v>77</v>
       </c>
       <c r="B80" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -2378,7 +2378,7 @@
         <v>78</v>
       </c>
       <c r="B81" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
@@ -2386,7 +2386,7 @@
         <v>79</v>
       </c>
       <c r="B82" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -2394,7 +2394,7 @@
         <v>80</v>
       </c>
       <c r="B83" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -2402,7 +2402,7 @@
         <v>81</v>
       </c>
       <c r="B84" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -2410,7 +2410,7 @@
         <v>82</v>
       </c>
       <c r="B85" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
@@ -2418,7 +2418,7 @@
         <v>83</v>
       </c>
       <c r="B86" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -2426,7 +2426,7 @@
         <v>84</v>
       </c>
       <c r="B87" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
@@ -2434,7 +2434,7 @@
         <v>85</v>
       </c>
       <c r="B88" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
@@ -2442,7 +2442,7 @@
         <v>86</v>
       </c>
       <c r="B89" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
@@ -2450,7 +2450,7 @@
         <v>87</v>
       </c>
       <c r="B90" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
@@ -2458,7 +2458,7 @@
         <v>88</v>
       </c>
       <c r="B91" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
@@ -2466,7 +2466,7 @@
         <v>89</v>
       </c>
       <c r="B92" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
@@ -2474,7 +2474,7 @@
         <v>90</v>
       </c>
       <c r="B93" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
@@ -2482,7 +2482,7 @@
         <v>91</v>
       </c>
       <c r="B94" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
@@ -2490,7 +2490,7 @@
         <v>92</v>
       </c>
       <c r="B95" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
@@ -2498,7 +2498,7 @@
         <v>93</v>
       </c>
       <c r="B96" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
@@ -2506,7 +2506,7 @@
         <v>94</v>
       </c>
       <c r="B97" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
@@ -2514,7 +2514,7 @@
         <v>95</v>
       </c>
       <c r="B98" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
@@ -2522,7 +2522,7 @@
         <v>96</v>
       </c>
       <c r="B99" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
@@ -2530,7 +2530,7 @@
         <v>97</v>
       </c>
       <c r="B100" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
@@ -2538,7 +2538,7 @@
         <v>98</v>
       </c>
       <c r="B101" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
@@ -2546,7 +2546,7 @@
         <v>99</v>
       </c>
       <c r="B102" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
@@ -2554,7 +2554,7 @@
         <v>100</v>
       </c>
       <c r="B103" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/LevelData.xlsx
+++ b/Excel/LevelData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Color\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0412A7FD-56D3-4162-A754-F980D6C59E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29A2972-DB69-48B1-80CF-2571B55CFCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3405" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2002,7 +2002,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -2010,7 +2010,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -2018,7 +2018,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -2026,7 +2026,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -2034,7 +2034,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -2042,7 +2042,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -2050,7 +2050,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -2058,7 +2058,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -2066,7 +2066,7 @@
         <v>39</v>
       </c>
       <c r="B42" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -2074,7 +2074,7 @@
         <v>40</v>
       </c>
       <c r="B43" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -2082,7 +2082,7 @@
         <v>41</v>
       </c>
       <c r="B44" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -2090,7 +2090,7 @@
         <v>42</v>
       </c>
       <c r="B45" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -2098,7 +2098,7 @@
         <v>43</v>
       </c>
       <c r="B46" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
@@ -2106,7 +2106,7 @@
         <v>44</v>
       </c>
       <c r="B47" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -2114,7 +2114,7 @@
         <v>45</v>
       </c>
       <c r="B48" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -2122,7 +2122,7 @@
         <v>46</v>
       </c>
       <c r="B49" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -2130,7 +2130,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -2138,7 +2138,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -2146,7 +2146,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -2154,7 +2154,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -2162,7 +2162,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -2170,7 +2170,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -2178,7 +2178,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -2186,7 +2186,7 @@
         <v>54</v>
       </c>
       <c r="B57" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -2194,7 +2194,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -2202,7 +2202,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -2210,7 +2210,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -2218,7 +2218,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -2226,7 +2226,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -2234,7 +2234,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -2242,7 +2242,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -2250,7 +2250,7 @@
         <v>62</v>
       </c>
       <c r="B65" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -2258,7 +2258,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -2266,7 +2266,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -2274,7 +2274,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
@@ -2282,7 +2282,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
@@ -2290,7 +2290,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
@@ -2298,7 +2298,7 @@
         <v>68</v>
       </c>
       <c r="B71" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
@@ -2306,7 +2306,7 @@
         <v>69</v>
       </c>
       <c r="B72" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -2314,7 +2314,7 @@
         <v>70</v>
       </c>
       <c r="B73" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
@@ -2322,7 +2322,7 @@
         <v>71</v>
       </c>
       <c r="B74" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
@@ -2330,7 +2330,7 @@
         <v>72</v>
       </c>
       <c r="B75" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -2338,7 +2338,7 @@
         <v>73</v>
       </c>
       <c r="B76" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -2346,7 +2346,7 @@
         <v>74</v>
       </c>
       <c r="B77" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -2354,7 +2354,7 @@
         <v>75</v>
       </c>
       <c r="B78" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -2362,7 +2362,7 @@
         <v>76</v>
       </c>
       <c r="B79" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
@@ -2370,7 +2370,7 @@
         <v>77</v>
       </c>
       <c r="B80" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -2378,7 +2378,7 @@
         <v>78</v>
       </c>
       <c r="B81" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
@@ -2386,7 +2386,7 @@
         <v>79</v>
       </c>
       <c r="B82" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -2394,7 +2394,7 @@
         <v>80</v>
       </c>
       <c r="B83" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -2402,7 +2402,7 @@
         <v>81</v>
       </c>
       <c r="B84" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -2410,7 +2410,7 @@
         <v>82</v>
       </c>
       <c r="B85" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
@@ -2418,7 +2418,7 @@
         <v>83</v>
       </c>
       <c r="B86" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -2426,7 +2426,7 @@
         <v>84</v>
       </c>
       <c r="B87" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
@@ -2434,7 +2434,7 @@
         <v>85</v>
       </c>
       <c r="B88" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
@@ -2442,7 +2442,7 @@
         <v>86</v>
       </c>
       <c r="B89" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
@@ -2450,7 +2450,7 @@
         <v>87</v>
       </c>
       <c r="B90" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
@@ -2458,7 +2458,7 @@
         <v>88</v>
       </c>
       <c r="B91" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
@@ -2466,7 +2466,7 @@
         <v>89</v>
       </c>
       <c r="B92" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
@@ -2474,7 +2474,7 @@
         <v>90</v>
       </c>
       <c r="B93" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
@@ -2482,7 +2482,7 @@
         <v>91</v>
       </c>
       <c r="B94" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
@@ -2490,7 +2490,7 @@
         <v>92</v>
       </c>
       <c r="B95" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
@@ -2498,7 +2498,7 @@
         <v>93</v>
       </c>
       <c r="B96" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
@@ -2506,7 +2506,7 @@
         <v>94</v>
       </c>
       <c r="B97" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
@@ -2514,7 +2514,7 @@
         <v>95</v>
       </c>
       <c r="B98" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
@@ -2522,7 +2522,7 @@
         <v>96</v>
       </c>
       <c r="B99" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
@@ -2530,7 +2530,7 @@
         <v>97</v>
       </c>
       <c r="B100" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
@@ -2538,7 +2538,7 @@
         <v>98</v>
       </c>
       <c r="B101" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
@@ -2546,7 +2546,7 @@
         <v>99</v>
       </c>
       <c r="B102" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
@@ -2554,7 +2554,7 @@
         <v>100</v>
       </c>
       <c r="B103" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/LevelData.xlsx
+++ b/Excel/LevelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Color\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29A2972-DB69-48B1-80CF-2571B55CFCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD59C9F7-174D-4404-8685-FCECCD0CE852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3405" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LevelData" sheetId="7" r:id="rId1"/>
@@ -470,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{893968D5-95F3-4D8C-9E27-761EA7BEA57E}">
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D203"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
@@ -1717,6 +1717,1206 @@
       </c>
       <c r="D103" s="7"/>
     </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="4">
+        <v>101</v>
+      </c>
+      <c r="B104" s="3">
+        <v>6</v>
+      </c>
+      <c r="C104">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D104" s="8"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="4">
+        <v>102</v>
+      </c>
+      <c r="B105" s="3">
+        <v>6</v>
+      </c>
+      <c r="C105">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D105" s="9"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="4">
+        <v>103</v>
+      </c>
+      <c r="B106" s="3">
+        <v>6</v>
+      </c>
+      <c r="C106">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D106" s="10"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="4">
+        <v>104</v>
+      </c>
+      <c r="B107" s="3">
+        <v>6</v>
+      </c>
+      <c r="C107">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D107" s="11"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="4">
+        <v>105</v>
+      </c>
+      <c r="B108" s="3">
+        <v>6</v>
+      </c>
+      <c r="C108">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D108" s="12"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="4">
+        <v>106</v>
+      </c>
+      <c r="B109" s="3">
+        <v>6</v>
+      </c>
+      <c r="C109">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D109" s="6"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="4">
+        <v>107</v>
+      </c>
+      <c r="B110" s="3">
+        <v>6</v>
+      </c>
+      <c r="C110">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D110" s="7"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="4">
+        <v>108</v>
+      </c>
+      <c r="B111" s="3">
+        <v>6</v>
+      </c>
+      <c r="C111">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D111" s="8"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="4">
+        <v>109</v>
+      </c>
+      <c r="B112" s="3">
+        <v>6</v>
+      </c>
+      <c r="C112">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D112" s="9"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="4">
+        <v>110</v>
+      </c>
+      <c r="B113" s="3">
+        <v>6</v>
+      </c>
+      <c r="C113">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D113" s="10"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="4">
+        <v>111</v>
+      </c>
+      <c r="B114" s="3">
+        <v>6</v>
+      </c>
+      <c r="C114">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D114" s="11"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="4">
+        <v>112</v>
+      </c>
+      <c r="B115" s="3">
+        <v>6</v>
+      </c>
+      <c r="C115">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D115" s="12"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="4">
+        <v>113</v>
+      </c>
+      <c r="B116" s="3">
+        <v>6</v>
+      </c>
+      <c r="C116">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D116" s="6"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="4">
+        <v>114</v>
+      </c>
+      <c r="B117" s="3">
+        <v>6</v>
+      </c>
+      <c r="C117">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D117" s="7"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="4">
+        <v>115</v>
+      </c>
+      <c r="B118" s="3">
+        <v>6</v>
+      </c>
+      <c r="C118">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D118" s="8"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" s="4">
+        <v>116</v>
+      </c>
+      <c r="B119" s="3">
+        <v>6</v>
+      </c>
+      <c r="C119">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D119" s="9"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" s="4">
+        <v>117</v>
+      </c>
+      <c r="B120" s="3">
+        <v>6</v>
+      </c>
+      <c r="C120">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D120" s="10"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="4">
+        <v>118</v>
+      </c>
+      <c r="B121" s="3">
+        <v>6</v>
+      </c>
+      <c r="C121">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D121" s="11"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" s="4">
+        <v>119</v>
+      </c>
+      <c r="B122" s="3">
+        <v>6</v>
+      </c>
+      <c r="C122">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D122" s="12"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="4">
+        <v>120</v>
+      </c>
+      <c r="B123" s="3">
+        <v>6</v>
+      </c>
+      <c r="C123">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D123" s="6"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="4">
+        <v>121</v>
+      </c>
+      <c r="B124" s="3">
+        <v>6</v>
+      </c>
+      <c r="C124">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D124" s="7"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" s="4">
+        <v>122</v>
+      </c>
+      <c r="B125" s="3">
+        <v>6</v>
+      </c>
+      <c r="C125">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D125" s="8"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" s="4">
+        <v>123</v>
+      </c>
+      <c r="B126" s="3">
+        <v>6</v>
+      </c>
+      <c r="C126">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D126" s="9"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" s="4">
+        <v>124</v>
+      </c>
+      <c r="B127" s="3">
+        <v>6</v>
+      </c>
+      <c r="C127">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D127" s="10"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="4">
+        <v>125</v>
+      </c>
+      <c r="B128" s="3">
+        <v>6</v>
+      </c>
+      <c r="C128">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D128" s="11"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="4">
+        <v>126</v>
+      </c>
+      <c r="B129" s="3">
+        <v>6</v>
+      </c>
+      <c r="C129">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D129" s="12"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" s="4">
+        <v>127</v>
+      </c>
+      <c r="B130" s="3">
+        <v>6</v>
+      </c>
+      <c r="C130">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D130" s="6"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" s="4">
+        <v>128</v>
+      </c>
+      <c r="B131" s="3">
+        <v>6</v>
+      </c>
+      <c r="C131">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D131" s="7"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="4">
+        <v>129</v>
+      </c>
+      <c r="B132" s="3">
+        <v>6</v>
+      </c>
+      <c r="C132">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D132" s="8"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" s="4">
+        <v>130</v>
+      </c>
+      <c r="B133" s="3">
+        <v>6</v>
+      </c>
+      <c r="C133">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D133" s="9"/>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="4">
+        <v>131</v>
+      </c>
+      <c r="B134" s="3">
+        <v>6</v>
+      </c>
+      <c r="C134">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D134" s="10"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="4">
+        <v>132</v>
+      </c>
+      <c r="B135" s="3">
+        <v>6</v>
+      </c>
+      <c r="C135">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D135" s="11"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" s="4">
+        <v>133</v>
+      </c>
+      <c r="B136" s="3">
+        <v>6</v>
+      </c>
+      <c r="C136">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D136" s="12"/>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" s="4">
+        <v>134</v>
+      </c>
+      <c r="B137" s="3">
+        <v>6</v>
+      </c>
+      <c r="C137">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D137" s="6"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" s="4">
+        <v>135</v>
+      </c>
+      <c r="B138" s="3">
+        <v>6</v>
+      </c>
+      <c r="C138">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D138" s="7"/>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139" s="4">
+        <v>136</v>
+      </c>
+      <c r="B139" s="3">
+        <v>6</v>
+      </c>
+      <c r="C139">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D139" s="8"/>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140" s="4">
+        <v>137</v>
+      </c>
+      <c r="B140" s="3">
+        <v>6</v>
+      </c>
+      <c r="C140">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D140" s="9"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141" s="4">
+        <v>138</v>
+      </c>
+      <c r="B141" s="3">
+        <v>6</v>
+      </c>
+      <c r="C141">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D141" s="10"/>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A142" s="4">
+        <v>139</v>
+      </c>
+      <c r="B142" s="3">
+        <v>6</v>
+      </c>
+      <c r="C142">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D142" s="11"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A143" s="4">
+        <v>140</v>
+      </c>
+      <c r="B143" s="3">
+        <v>6</v>
+      </c>
+      <c r="C143">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D143" s="12"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A144" s="4">
+        <v>141</v>
+      </c>
+      <c r="B144" s="3">
+        <v>6</v>
+      </c>
+      <c r="C144">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D144" s="6"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145" s="4">
+        <v>142</v>
+      </c>
+      <c r="B145" s="3">
+        <v>6</v>
+      </c>
+      <c r="C145">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D145" s="7"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146" s="4">
+        <v>143</v>
+      </c>
+      <c r="B146" s="3">
+        <v>6</v>
+      </c>
+      <c r="C146">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D146" s="8"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" s="4">
+        <v>144</v>
+      </c>
+      <c r="B147" s="3">
+        <v>6</v>
+      </c>
+      <c r="C147">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D147" s="9"/>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" s="4">
+        <v>145</v>
+      </c>
+      <c r="B148" s="3">
+        <v>6</v>
+      </c>
+      <c r="C148">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D148" s="10"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" s="4">
+        <v>146</v>
+      </c>
+      <c r="B149" s="3">
+        <v>6</v>
+      </c>
+      <c r="C149">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D149" s="11"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" s="4">
+        <v>147</v>
+      </c>
+      <c r="B150" s="3">
+        <v>6</v>
+      </c>
+      <c r="C150">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D150" s="12"/>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" s="4">
+        <v>148</v>
+      </c>
+      <c r="B151" s="3">
+        <v>6</v>
+      </c>
+      <c r="C151">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D151" s="6"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" s="4">
+        <v>149</v>
+      </c>
+      <c r="B152" s="3">
+        <v>6</v>
+      </c>
+      <c r="C152">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D152" s="7"/>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" s="4">
+        <v>150</v>
+      </c>
+      <c r="B153" s="3">
+        <v>6</v>
+      </c>
+      <c r="C153">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D153" s="8"/>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A154" s="4">
+        <v>151</v>
+      </c>
+      <c r="B154" s="3">
+        <v>6</v>
+      </c>
+      <c r="C154">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D154" s="9"/>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A155" s="4">
+        <v>152</v>
+      </c>
+      <c r="B155" s="3">
+        <v>6</v>
+      </c>
+      <c r="C155">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D155" s="10"/>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156" s="4">
+        <v>153</v>
+      </c>
+      <c r="B156" s="3">
+        <v>6</v>
+      </c>
+      <c r="C156">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D156" s="11"/>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157" s="4">
+        <v>154</v>
+      </c>
+      <c r="B157" s="3">
+        <v>6</v>
+      </c>
+      <c r="C157">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D157" s="12"/>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158" s="4">
+        <v>155</v>
+      </c>
+      <c r="B158" s="3">
+        <v>6</v>
+      </c>
+      <c r="C158">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D158" s="6"/>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159" s="4">
+        <v>156</v>
+      </c>
+      <c r="B159" s="3">
+        <v>6</v>
+      </c>
+      <c r="C159">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D159" s="7"/>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A160" s="4">
+        <v>157</v>
+      </c>
+      <c r="B160" s="3">
+        <v>6</v>
+      </c>
+      <c r="C160">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D160" s="8"/>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" s="4">
+        <v>158</v>
+      </c>
+      <c r="B161" s="3">
+        <v>6</v>
+      </c>
+      <c r="C161">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D161" s="9"/>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" s="4">
+        <v>159</v>
+      </c>
+      <c r="B162" s="3">
+        <v>6</v>
+      </c>
+      <c r="C162">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D162" s="10"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" s="4">
+        <v>160</v>
+      </c>
+      <c r="B163" s="3">
+        <v>6</v>
+      </c>
+      <c r="C163">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D163" s="11"/>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A164" s="4">
+        <v>161</v>
+      </c>
+      <c r="B164" s="3">
+        <v>6</v>
+      </c>
+      <c r="C164">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D164" s="12"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165" s="4">
+        <v>162</v>
+      </c>
+      <c r="B165" s="3">
+        <v>6</v>
+      </c>
+      <c r="C165">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D165" s="6"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A166" s="4">
+        <v>163</v>
+      </c>
+      <c r="B166" s="3">
+        <v>6</v>
+      </c>
+      <c r="C166">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D166" s="7"/>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A167" s="4">
+        <v>164</v>
+      </c>
+      <c r="B167" s="3">
+        <v>6</v>
+      </c>
+      <c r="C167">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D167" s="8"/>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A168" s="4">
+        <v>165</v>
+      </c>
+      <c r="B168" s="3">
+        <v>6</v>
+      </c>
+      <c r="C168">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D168" s="9"/>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A169" s="4">
+        <v>166</v>
+      </c>
+      <c r="B169" s="3">
+        <v>6</v>
+      </c>
+      <c r="C169">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D169" s="10"/>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A170" s="4">
+        <v>167</v>
+      </c>
+      <c r="B170" s="3">
+        <v>6</v>
+      </c>
+      <c r="C170">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D170" s="11"/>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A171" s="4">
+        <v>168</v>
+      </c>
+      <c r="B171" s="3">
+        <v>6</v>
+      </c>
+      <c r="C171">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D171" s="12"/>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172" s="4">
+        <v>169</v>
+      </c>
+      <c r="B172" s="3">
+        <v>6</v>
+      </c>
+      <c r="C172">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D172" s="6"/>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173" s="4">
+        <v>170</v>
+      </c>
+      <c r="B173" s="3">
+        <v>6</v>
+      </c>
+      <c r="C173">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D173" s="7"/>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A174" s="4">
+        <v>171</v>
+      </c>
+      <c r="B174" s="3">
+        <v>6</v>
+      </c>
+      <c r="C174">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D174" s="8"/>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A175" s="4">
+        <v>172</v>
+      </c>
+      <c r="B175" s="3">
+        <v>6</v>
+      </c>
+      <c r="C175">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D175" s="9"/>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A176" s="4">
+        <v>173</v>
+      </c>
+      <c r="B176" s="3">
+        <v>6</v>
+      </c>
+      <c r="C176">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D176" s="10"/>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" s="4">
+        <v>174</v>
+      </c>
+      <c r="B177" s="3">
+        <v>6</v>
+      </c>
+      <c r="C177">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D177" s="11"/>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178" s="4">
+        <v>175</v>
+      </c>
+      <c r="B178" s="3">
+        <v>6</v>
+      </c>
+      <c r="C178">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D178" s="12"/>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A179" s="4">
+        <v>176</v>
+      </c>
+      <c r="B179" s="3">
+        <v>6</v>
+      </c>
+      <c r="C179">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D179" s="6"/>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A180" s="4">
+        <v>177</v>
+      </c>
+      <c r="B180" s="3">
+        <v>6</v>
+      </c>
+      <c r="C180">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D180" s="7"/>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A181" s="4">
+        <v>178</v>
+      </c>
+      <c r="B181" s="3">
+        <v>6</v>
+      </c>
+      <c r="C181">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D181" s="8"/>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A182" s="4">
+        <v>179</v>
+      </c>
+      <c r="B182" s="3">
+        <v>6</v>
+      </c>
+      <c r="C182">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D182" s="9"/>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" s="4">
+        <v>180</v>
+      </c>
+      <c r="B183" s="3">
+        <v>6</v>
+      </c>
+      <c r="C183">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D183" s="10"/>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A184" s="4">
+        <v>181</v>
+      </c>
+      <c r="B184" s="3">
+        <v>6</v>
+      </c>
+      <c r="C184">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D184" s="11"/>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A185" s="4">
+        <v>182</v>
+      </c>
+      <c r="B185" s="3">
+        <v>6</v>
+      </c>
+      <c r="C185">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D185" s="12"/>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186" s="4">
+        <v>183</v>
+      </c>
+      <c r="B186" s="3">
+        <v>6</v>
+      </c>
+      <c r="C186">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D186" s="6"/>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A187" s="4">
+        <v>184</v>
+      </c>
+      <c r="B187" s="3">
+        <v>6</v>
+      </c>
+      <c r="C187">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D187" s="7"/>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A188" s="4">
+        <v>185</v>
+      </c>
+      <c r="B188" s="3">
+        <v>6</v>
+      </c>
+      <c r="C188">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D188" s="8"/>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A189" s="4">
+        <v>186</v>
+      </c>
+      <c r="B189" s="3">
+        <v>6</v>
+      </c>
+      <c r="C189">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D189" s="9"/>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A190" s="4">
+        <v>187</v>
+      </c>
+      <c r="B190" s="3">
+        <v>6</v>
+      </c>
+      <c r="C190">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D190" s="10"/>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A191" s="4">
+        <v>188</v>
+      </c>
+      <c r="B191" s="3">
+        <v>6</v>
+      </c>
+      <c r="C191">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D191" s="11"/>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A192" s="4">
+        <v>189</v>
+      </c>
+      <c r="B192" s="3">
+        <v>6</v>
+      </c>
+      <c r="C192">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D192" s="12"/>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A193" s="4">
+        <v>190</v>
+      </c>
+      <c r="B193" s="3">
+        <v>6</v>
+      </c>
+      <c r="C193">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D193" s="6"/>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A194" s="4">
+        <v>191</v>
+      </c>
+      <c r="B194" s="3">
+        <v>6</v>
+      </c>
+      <c r="C194">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D194" s="7"/>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A195" s="4">
+        <v>192</v>
+      </c>
+      <c r="B195" s="3">
+        <v>6</v>
+      </c>
+      <c r="C195">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D195" s="8"/>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A196" s="4">
+        <v>193</v>
+      </c>
+      <c r="B196" s="3">
+        <v>6</v>
+      </c>
+      <c r="C196">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D196" s="9"/>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A197" s="4">
+        <v>194</v>
+      </c>
+      <c r="B197" s="3">
+        <v>6</v>
+      </c>
+      <c r="C197">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D197" s="10"/>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A198" s="4">
+        <v>195</v>
+      </c>
+      <c r="B198" s="3">
+        <v>6</v>
+      </c>
+      <c r="C198">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D198" s="11"/>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A199" s="4">
+        <v>196</v>
+      </c>
+      <c r="B199" s="3">
+        <v>6</v>
+      </c>
+      <c r="C199">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D199" s="12"/>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A200" s="4">
+        <v>197</v>
+      </c>
+      <c r="B200" s="3">
+        <v>6</v>
+      </c>
+      <c r="C200">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D200" s="6"/>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A201" s="4">
+        <v>198</v>
+      </c>
+      <c r="B201" s="3">
+        <v>6</v>
+      </c>
+      <c r="C201">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D201" s="7"/>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A202" s="4">
+        <v>199</v>
+      </c>
+      <c r="B202" s="3">
+        <v>6</v>
+      </c>
+      <c r="C202">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D202" s="8"/>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A203" s="4">
+        <v>200</v>
+      </c>
+      <c r="B203" s="3">
+        <v>6</v>
+      </c>
+      <c r="C203">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D203" s="9"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1726,7 +2926,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FBBFF61-F2A9-4270-86EF-F5F8D76F72F6}">
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B207"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1834,7 +3034,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -1842,7 +3042,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -1850,7 +3050,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -1858,7 +3058,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -1866,7 +3066,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -1874,7 +3074,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -1882,7 +3082,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -1890,7 +3090,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -1898,7 +3098,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -1906,7 +3106,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -1914,7 +3114,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -1922,7 +3122,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -1930,7 +3130,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -1938,7 +3138,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -1946,7 +3146,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -1954,7 +3154,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -1962,7 +3162,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -1970,7 +3170,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -1978,7 +3178,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -1986,7 +3186,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -1994,7 +3194,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -2556,6 +3756,822 @@
       <c r="B103" s="5">
         <v>4</v>
       </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="4">
+        <v>101</v>
+      </c>
+      <c r="B104" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" s="4">
+        <v>102</v>
+      </c>
+      <c r="B105" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" s="4">
+        <v>103</v>
+      </c>
+      <c r="B106" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="4">
+        <v>104</v>
+      </c>
+      <c r="B107" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" s="4">
+        <v>105</v>
+      </c>
+      <c r="B108" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" s="4">
+        <v>106</v>
+      </c>
+      <c r="B109" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="4">
+        <v>107</v>
+      </c>
+      <c r="B110" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="4">
+        <v>108</v>
+      </c>
+      <c r="B111" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="4">
+        <v>109</v>
+      </c>
+      <c r="B112" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" s="4">
+        <v>110</v>
+      </c>
+      <c r="B113" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" s="4">
+        <v>111</v>
+      </c>
+      <c r="B114" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" s="4">
+        <v>112</v>
+      </c>
+      <c r="B115" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" s="4">
+        <v>113</v>
+      </c>
+      <c r="B116" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" s="4">
+        <v>114</v>
+      </c>
+      <c r="B117" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" s="4">
+        <v>115</v>
+      </c>
+      <c r="B118" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" s="4">
+        <v>116</v>
+      </c>
+      <c r="B119" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" s="4">
+        <v>117</v>
+      </c>
+      <c r="B120" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" s="4">
+        <v>118</v>
+      </c>
+      <c r="B121" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" s="4">
+        <v>119</v>
+      </c>
+      <c r="B122" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" s="4">
+        <v>120</v>
+      </c>
+      <c r="B123" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" s="4">
+        <v>121</v>
+      </c>
+      <c r="B124" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" s="4">
+        <v>122</v>
+      </c>
+      <c r="B125" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" s="4">
+        <v>123</v>
+      </c>
+      <c r="B126" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" s="4">
+        <v>124</v>
+      </c>
+      <c r="B127" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" s="4">
+        <v>125</v>
+      </c>
+      <c r="B128" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" s="4">
+        <v>126</v>
+      </c>
+      <c r="B129" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" s="4">
+        <v>127</v>
+      </c>
+      <c r="B130" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" s="4">
+        <v>128</v>
+      </c>
+      <c r="B131" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" s="4">
+        <v>129</v>
+      </c>
+      <c r="B132" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" s="4">
+        <v>130</v>
+      </c>
+      <c r="B133" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" s="4">
+        <v>131</v>
+      </c>
+      <c r="B134" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" s="4">
+        <v>132</v>
+      </c>
+      <c r="B135" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" s="4">
+        <v>133</v>
+      </c>
+      <c r="B136" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" s="4">
+        <v>134</v>
+      </c>
+      <c r="B137" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" s="4">
+        <v>135</v>
+      </c>
+      <c r="B138" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" s="4">
+        <v>136</v>
+      </c>
+      <c r="B139" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" s="4">
+        <v>137</v>
+      </c>
+      <c r="B140" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" s="4">
+        <v>138</v>
+      </c>
+      <c r="B141" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" s="4">
+        <v>139</v>
+      </c>
+      <c r="B142" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" s="4">
+        <v>140</v>
+      </c>
+      <c r="B143" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" s="4">
+        <v>141</v>
+      </c>
+      <c r="B144" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" s="4">
+        <v>142</v>
+      </c>
+      <c r="B145" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" s="4">
+        <v>143</v>
+      </c>
+      <c r="B146" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" s="4">
+        <v>144</v>
+      </c>
+      <c r="B147" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" s="4">
+        <v>145</v>
+      </c>
+      <c r="B148" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" s="4">
+        <v>146</v>
+      </c>
+      <c r="B149" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" s="4">
+        <v>147</v>
+      </c>
+      <c r="B150" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" s="4">
+        <v>148</v>
+      </c>
+      <c r="B151" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" s="4">
+        <v>149</v>
+      </c>
+      <c r="B152" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" s="4">
+        <v>150</v>
+      </c>
+      <c r="B153" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" s="4">
+        <v>151</v>
+      </c>
+      <c r="B154" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" s="4">
+        <v>152</v>
+      </c>
+      <c r="B155" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" s="4">
+        <v>153</v>
+      </c>
+      <c r="B156" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" s="4">
+        <v>154</v>
+      </c>
+      <c r="B157" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" s="4">
+        <v>155</v>
+      </c>
+      <c r="B158" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" s="4">
+        <v>156</v>
+      </c>
+      <c r="B159" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" s="4">
+        <v>157</v>
+      </c>
+      <c r="B160" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" s="4">
+        <v>158</v>
+      </c>
+      <c r="B161" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" s="4">
+        <v>159</v>
+      </c>
+      <c r="B162" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" s="4">
+        <v>160</v>
+      </c>
+      <c r="B163" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" s="4">
+        <v>161</v>
+      </c>
+      <c r="B164" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" s="4">
+        <v>162</v>
+      </c>
+      <c r="B165" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" s="4">
+        <v>163</v>
+      </c>
+      <c r="B166" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" s="4">
+        <v>164</v>
+      </c>
+      <c r="B167" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" s="4">
+        <v>165</v>
+      </c>
+      <c r="B168" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" s="4">
+        <v>166</v>
+      </c>
+      <c r="B169" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" s="4">
+        <v>167</v>
+      </c>
+      <c r="B170" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" s="4">
+        <v>168</v>
+      </c>
+      <c r="B171" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" s="4">
+        <v>169</v>
+      </c>
+      <c r="B172" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" s="4">
+        <v>170</v>
+      </c>
+      <c r="B173" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" s="4">
+        <v>171</v>
+      </c>
+      <c r="B174" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" s="4">
+        <v>172</v>
+      </c>
+      <c r="B175" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" s="4">
+        <v>173</v>
+      </c>
+      <c r="B176" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" s="4">
+        <v>174</v>
+      </c>
+      <c r="B177" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" s="4">
+        <v>175</v>
+      </c>
+      <c r="B178" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" s="4">
+        <v>176</v>
+      </c>
+      <c r="B179" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" s="4">
+        <v>177</v>
+      </c>
+      <c r="B180" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" s="4">
+        <v>178</v>
+      </c>
+      <c r="B181" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" s="4">
+        <v>179</v>
+      </c>
+      <c r="B182" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" s="4">
+        <v>180</v>
+      </c>
+      <c r="B183" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" s="4">
+        <v>181</v>
+      </c>
+      <c r="B184" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" s="4">
+        <v>182</v>
+      </c>
+      <c r="B185" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" s="4">
+        <v>183</v>
+      </c>
+      <c r="B186" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" s="4">
+        <v>184</v>
+      </c>
+      <c r="B187" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" s="4">
+        <v>185</v>
+      </c>
+      <c r="B188" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" s="4">
+        <v>186</v>
+      </c>
+      <c r="B189" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" s="4">
+        <v>187</v>
+      </c>
+      <c r="B190" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" s="4">
+        <v>188</v>
+      </c>
+      <c r="B191" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" s="4">
+        <v>189</v>
+      </c>
+      <c r="B192" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" s="4">
+        <v>190</v>
+      </c>
+      <c r="B193" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" s="4">
+        <v>191</v>
+      </c>
+      <c r="B194" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" s="4">
+        <v>192</v>
+      </c>
+      <c r="B195" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" s="4">
+        <v>193</v>
+      </c>
+      <c r="B196" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" s="4">
+        <v>194</v>
+      </c>
+      <c r="B197" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" s="4">
+        <v>195</v>
+      </c>
+      <c r="B198" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" s="4">
+        <v>196</v>
+      </c>
+      <c r="B199" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" s="4">
+        <v>197</v>
+      </c>
+      <c r="B200" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" s="4">
+        <v>198</v>
+      </c>
+      <c r="B201" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" s="4">
+        <v>199</v>
+      </c>
+      <c r="B202" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" s="4">
+        <v>200</v>
+      </c>
+      <c r="B203" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204" s="4"/>
+      <c r="B204" s="5"/>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" s="4"/>
+      <c r="B205" s="5"/>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" s="4"/>
+      <c r="B206" s="5"/>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" s="4"/>
+      <c r="B207" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Excel/LevelData.xlsx
+++ b/Excel/LevelData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Color\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD59C9F7-174D-4404-8685-FCECCD0CE852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365D61D7-8B49-4FA8-8CDE-28FACEADBC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -470,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{893968D5-95F3-4D8C-9E27-761EA7BEA57E}">
-  <dimension ref="A1:D203"/>
+  <dimension ref="A1:D403"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
@@ -549,7 +549,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="D6" s="8"/>
     </row>
@@ -633,7 +633,7 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="D13" s="8"/>
     </row>
@@ -717,7 +717,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="D20" s="8"/>
     </row>
@@ -801,7 +801,7 @@
         <v>6</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="D27" s="8"/>
     </row>
@@ -885,7 +885,7 @@
         <v>6</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="D34" s="8"/>
     </row>
@@ -969,7 +969,7 @@
         <v>6</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="D41" s="8"/>
     </row>
@@ -1053,7 +1053,7 @@
         <v>6</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="D48" s="8"/>
     </row>
@@ -1137,7 +1137,7 @@
         <v>6</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D55" s="8"/>
     </row>
@@ -1221,7 +1221,7 @@
         <v>6</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="D62" s="8"/>
     </row>
@@ -1305,7 +1305,7 @@
         <v>6</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="D69" s="8"/>
     </row>
@@ -1389,7 +1389,7 @@
         <v>6</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="D76" s="8"/>
     </row>
@@ -1473,7 +1473,7 @@
         <v>6</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>0.22</v>
       </c>
       <c r="D83" s="8"/>
     </row>
@@ -1557,7 +1557,7 @@
         <v>6</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="D90" s="8"/>
     </row>
@@ -1641,7 +1641,7 @@
         <v>6</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="D97" s="8"/>
     </row>
@@ -2916,6 +2916,2406 @@
         <v>9.9999999999999006E-2</v>
       </c>
       <c r="D203" s="9"/>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A204" s="4">
+        <v>201</v>
+      </c>
+      <c r="B204" s="3">
+        <v>6</v>
+      </c>
+      <c r="C204">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D204" s="10"/>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A205" s="4">
+        <v>202</v>
+      </c>
+      <c r="B205" s="3">
+        <v>6</v>
+      </c>
+      <c r="C205">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D205" s="11"/>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A206" s="4">
+        <v>203</v>
+      </c>
+      <c r="B206" s="3">
+        <v>6</v>
+      </c>
+      <c r="C206">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D206" s="12"/>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A207" s="4">
+        <v>204</v>
+      </c>
+      <c r="B207" s="3">
+        <v>6</v>
+      </c>
+      <c r="C207">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D207" s="6"/>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A208" s="4">
+        <v>205</v>
+      </c>
+      <c r="B208" s="3">
+        <v>6</v>
+      </c>
+      <c r="C208">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D208" s="7"/>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A209" s="4">
+        <v>206</v>
+      </c>
+      <c r="B209" s="3">
+        <v>6</v>
+      </c>
+      <c r="C209">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D209" s="8"/>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A210" s="4">
+        <v>207</v>
+      </c>
+      <c r="B210" s="3">
+        <v>6</v>
+      </c>
+      <c r="C210">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D210" s="9"/>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A211" s="4">
+        <v>208</v>
+      </c>
+      <c r="B211" s="3">
+        <v>6</v>
+      </c>
+      <c r="C211">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D211" s="10"/>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A212" s="4">
+        <v>209</v>
+      </c>
+      <c r="B212" s="3">
+        <v>6</v>
+      </c>
+      <c r="C212">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D212" s="11"/>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A213" s="4">
+        <v>210</v>
+      </c>
+      <c r="B213" s="3">
+        <v>6</v>
+      </c>
+      <c r="C213">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D213" s="12"/>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A214" s="4">
+        <v>211</v>
+      </c>
+      <c r="B214" s="3">
+        <v>6</v>
+      </c>
+      <c r="C214">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D214" s="6"/>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A215" s="4">
+        <v>212</v>
+      </c>
+      <c r="B215" s="3">
+        <v>6</v>
+      </c>
+      <c r="C215">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D215" s="7"/>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A216" s="4">
+        <v>213</v>
+      </c>
+      <c r="B216" s="3">
+        <v>6</v>
+      </c>
+      <c r="C216">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D216" s="8"/>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A217" s="4">
+        <v>214</v>
+      </c>
+      <c r="B217" s="3">
+        <v>6</v>
+      </c>
+      <c r="C217">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D217" s="9"/>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A218" s="4">
+        <v>215</v>
+      </c>
+      <c r="B218" s="3">
+        <v>6</v>
+      </c>
+      <c r="C218">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D218" s="10"/>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A219" s="4">
+        <v>216</v>
+      </c>
+      <c r="B219" s="3">
+        <v>6</v>
+      </c>
+      <c r="C219">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D219" s="11"/>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A220" s="4">
+        <v>217</v>
+      </c>
+      <c r="B220" s="3">
+        <v>6</v>
+      </c>
+      <c r="C220">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D220" s="12"/>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A221" s="4">
+        <v>218</v>
+      </c>
+      <c r="B221" s="3">
+        <v>6</v>
+      </c>
+      <c r="C221">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D221" s="6"/>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A222" s="4">
+        <v>219</v>
+      </c>
+      <c r="B222" s="3">
+        <v>6</v>
+      </c>
+      <c r="C222">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D222" s="7"/>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A223" s="4">
+        <v>220</v>
+      </c>
+      <c r="B223" s="3">
+        <v>6</v>
+      </c>
+      <c r="C223">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D223" s="8"/>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A224" s="4">
+        <v>221</v>
+      </c>
+      <c r="B224" s="3">
+        <v>6</v>
+      </c>
+      <c r="C224">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D224" s="9"/>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A225" s="4">
+        <v>222</v>
+      </c>
+      <c r="B225" s="3">
+        <v>6</v>
+      </c>
+      <c r="C225">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D225" s="10"/>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A226" s="4">
+        <v>223</v>
+      </c>
+      <c r="B226" s="3">
+        <v>6</v>
+      </c>
+      <c r="C226">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D226" s="11"/>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A227" s="4">
+        <v>224</v>
+      </c>
+      <c r="B227" s="3">
+        <v>6</v>
+      </c>
+      <c r="C227">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D227" s="12"/>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A228" s="4">
+        <v>225</v>
+      </c>
+      <c r="B228" s="3">
+        <v>6</v>
+      </c>
+      <c r="C228">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D228" s="6"/>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A229" s="4">
+        <v>226</v>
+      </c>
+      <c r="B229" s="3">
+        <v>6</v>
+      </c>
+      <c r="C229">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D229" s="7"/>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A230" s="4">
+        <v>227</v>
+      </c>
+      <c r="B230" s="3">
+        <v>6</v>
+      </c>
+      <c r="C230">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D230" s="8"/>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A231" s="4">
+        <v>228</v>
+      </c>
+      <c r="B231" s="3">
+        <v>6</v>
+      </c>
+      <c r="C231">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D231" s="9"/>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A232" s="4">
+        <v>229</v>
+      </c>
+      <c r="B232" s="3">
+        <v>6</v>
+      </c>
+      <c r="C232">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D232" s="10"/>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A233" s="4">
+        <v>230</v>
+      </c>
+      <c r="B233" s="3">
+        <v>6</v>
+      </c>
+      <c r="C233">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D233" s="11"/>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A234" s="4">
+        <v>231</v>
+      </c>
+      <c r="B234" s="3">
+        <v>6</v>
+      </c>
+      <c r="C234">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D234" s="12"/>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A235" s="4">
+        <v>232</v>
+      </c>
+      <c r="B235" s="3">
+        <v>6</v>
+      </c>
+      <c r="C235">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D235" s="6"/>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A236" s="4">
+        <v>233</v>
+      </c>
+      <c r="B236" s="3">
+        <v>6</v>
+      </c>
+      <c r="C236">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D236" s="7"/>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A237" s="4">
+        <v>234</v>
+      </c>
+      <c r="B237" s="3">
+        <v>6</v>
+      </c>
+      <c r="C237">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D237" s="8"/>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A238" s="4">
+        <v>235</v>
+      </c>
+      <c r="B238" s="3">
+        <v>6</v>
+      </c>
+      <c r="C238">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D238" s="9"/>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A239" s="4">
+        <v>236</v>
+      </c>
+      <c r="B239" s="3">
+        <v>6</v>
+      </c>
+      <c r="C239">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D239" s="10"/>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A240" s="4">
+        <v>237</v>
+      </c>
+      <c r="B240" s="3">
+        <v>6</v>
+      </c>
+      <c r="C240">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D240" s="11"/>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A241" s="4">
+        <v>238</v>
+      </c>
+      <c r="B241" s="3">
+        <v>6</v>
+      </c>
+      <c r="C241">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D241" s="12"/>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A242" s="4">
+        <v>239</v>
+      </c>
+      <c r="B242" s="3">
+        <v>6</v>
+      </c>
+      <c r="C242">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D242" s="6"/>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A243" s="4">
+        <v>240</v>
+      </c>
+      <c r="B243" s="3">
+        <v>6</v>
+      </c>
+      <c r="C243">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D243" s="7"/>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A244" s="4">
+        <v>241</v>
+      </c>
+      <c r="B244" s="3">
+        <v>6</v>
+      </c>
+      <c r="C244">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D244" s="8"/>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A245" s="4">
+        <v>242</v>
+      </c>
+      <c r="B245" s="3">
+        <v>6</v>
+      </c>
+      <c r="C245">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D245" s="9"/>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A246" s="4">
+        <v>243</v>
+      </c>
+      <c r="B246" s="3">
+        <v>6</v>
+      </c>
+      <c r="C246">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D246" s="10"/>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A247" s="4">
+        <v>244</v>
+      </c>
+      <c r="B247" s="3">
+        <v>6</v>
+      </c>
+      <c r="C247">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D247" s="11"/>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A248" s="4">
+        <v>245</v>
+      </c>
+      <c r="B248" s="3">
+        <v>6</v>
+      </c>
+      <c r="C248">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D248" s="12"/>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A249" s="4">
+        <v>246</v>
+      </c>
+      <c r="B249" s="3">
+        <v>6</v>
+      </c>
+      <c r="C249">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D249" s="6"/>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A250" s="4">
+        <v>247</v>
+      </c>
+      <c r="B250" s="3">
+        <v>6</v>
+      </c>
+      <c r="C250">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D250" s="7"/>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A251" s="4">
+        <v>248</v>
+      </c>
+      <c r="B251" s="3">
+        <v>6</v>
+      </c>
+      <c r="C251">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D251" s="8"/>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A252" s="4">
+        <v>249</v>
+      </c>
+      <c r="B252" s="3">
+        <v>6</v>
+      </c>
+      <c r="C252">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D252" s="9"/>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A253" s="4">
+        <v>250</v>
+      </c>
+      <c r="B253" s="3">
+        <v>6</v>
+      </c>
+      <c r="C253">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D253" s="10"/>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A254" s="4">
+        <v>251</v>
+      </c>
+      <c r="B254" s="3">
+        <v>6</v>
+      </c>
+      <c r="C254">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D254" s="11"/>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A255" s="4">
+        <v>252</v>
+      </c>
+      <c r="B255" s="3">
+        <v>6</v>
+      </c>
+      <c r="C255">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D255" s="12"/>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A256" s="4">
+        <v>253</v>
+      </c>
+      <c r="B256" s="3">
+        <v>6</v>
+      </c>
+      <c r="C256">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D256" s="6"/>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A257" s="4">
+        <v>254</v>
+      </c>
+      <c r="B257" s="3">
+        <v>6</v>
+      </c>
+      <c r="C257">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D257" s="7"/>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A258" s="4">
+        <v>255</v>
+      </c>
+      <c r="B258" s="3">
+        <v>6</v>
+      </c>
+      <c r="C258">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D258" s="8"/>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A259" s="4">
+        <v>256</v>
+      </c>
+      <c r="B259" s="3">
+        <v>6</v>
+      </c>
+      <c r="C259">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D259" s="9"/>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A260" s="4">
+        <v>257</v>
+      </c>
+      <c r="B260" s="3">
+        <v>6</v>
+      </c>
+      <c r="C260">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D260" s="10"/>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A261" s="4">
+        <v>258</v>
+      </c>
+      <c r="B261" s="3">
+        <v>6</v>
+      </c>
+      <c r="C261">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D261" s="11"/>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A262" s="4">
+        <v>259</v>
+      </c>
+      <c r="B262" s="3">
+        <v>6</v>
+      </c>
+      <c r="C262">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D262" s="12"/>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A263" s="4">
+        <v>260</v>
+      </c>
+      <c r="B263" s="3">
+        <v>6</v>
+      </c>
+      <c r="C263">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D263" s="6"/>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A264" s="4">
+        <v>261</v>
+      </c>
+      <c r="B264" s="3">
+        <v>6</v>
+      </c>
+      <c r="C264">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D264" s="7"/>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A265" s="4">
+        <v>262</v>
+      </c>
+      <c r="B265" s="3">
+        <v>6</v>
+      </c>
+      <c r="C265">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D265" s="8"/>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A266" s="4">
+        <v>263</v>
+      </c>
+      <c r="B266" s="3">
+        <v>6</v>
+      </c>
+      <c r="C266">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D266" s="9"/>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A267" s="4">
+        <v>264</v>
+      </c>
+      <c r="B267" s="3">
+        <v>6</v>
+      </c>
+      <c r="C267">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D267" s="10"/>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A268" s="4">
+        <v>265</v>
+      </c>
+      <c r="B268" s="3">
+        <v>6</v>
+      </c>
+      <c r="C268">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D268" s="11"/>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A269" s="4">
+        <v>266</v>
+      </c>
+      <c r="B269" s="3">
+        <v>6</v>
+      </c>
+      <c r="C269">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D269" s="12"/>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A270" s="4">
+        <v>267</v>
+      </c>
+      <c r="B270" s="3">
+        <v>6</v>
+      </c>
+      <c r="C270">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D270" s="6"/>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A271" s="4">
+        <v>268</v>
+      </c>
+      <c r="B271" s="3">
+        <v>6</v>
+      </c>
+      <c r="C271">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D271" s="7"/>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A272" s="4">
+        <v>269</v>
+      </c>
+      <c r="B272" s="3">
+        <v>6</v>
+      </c>
+      <c r="C272">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D272" s="8"/>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A273" s="4">
+        <v>270</v>
+      </c>
+      <c r="B273" s="3">
+        <v>6</v>
+      </c>
+      <c r="C273">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D273" s="9"/>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A274" s="4">
+        <v>271</v>
+      </c>
+      <c r="B274" s="3">
+        <v>6</v>
+      </c>
+      <c r="C274">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D274" s="10"/>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A275" s="4">
+        <v>272</v>
+      </c>
+      <c r="B275" s="3">
+        <v>6</v>
+      </c>
+      <c r="C275">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D275" s="11"/>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A276" s="4">
+        <v>273</v>
+      </c>
+      <c r="B276" s="3">
+        <v>6</v>
+      </c>
+      <c r="C276">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D276" s="12"/>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A277" s="4">
+        <v>274</v>
+      </c>
+      <c r="B277" s="3">
+        <v>6</v>
+      </c>
+      <c r="C277">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D277" s="6"/>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A278" s="4">
+        <v>275</v>
+      </c>
+      <c r="B278" s="3">
+        <v>6</v>
+      </c>
+      <c r="C278">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D278" s="7"/>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A279" s="4">
+        <v>276</v>
+      </c>
+      <c r="B279" s="3">
+        <v>6</v>
+      </c>
+      <c r="C279">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D279" s="8"/>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A280" s="4">
+        <v>277</v>
+      </c>
+      <c r="B280" s="3">
+        <v>6</v>
+      </c>
+      <c r="C280">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D280" s="9"/>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A281" s="4">
+        <v>278</v>
+      </c>
+      <c r="B281" s="3">
+        <v>6</v>
+      </c>
+      <c r="C281">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D281" s="10"/>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A282" s="4">
+        <v>279</v>
+      </c>
+      <c r="B282" s="3">
+        <v>6</v>
+      </c>
+      <c r="C282">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D282" s="11"/>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A283" s="4">
+        <v>280</v>
+      </c>
+      <c r="B283" s="3">
+        <v>6</v>
+      </c>
+      <c r="C283">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D283" s="12"/>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A284" s="4">
+        <v>281</v>
+      </c>
+      <c r="B284" s="3">
+        <v>6</v>
+      </c>
+      <c r="C284">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D284" s="6"/>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A285" s="4">
+        <v>282</v>
+      </c>
+      <c r="B285" s="3">
+        <v>6</v>
+      </c>
+      <c r="C285">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D285" s="7"/>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A286" s="4">
+        <v>283</v>
+      </c>
+      <c r="B286" s="3">
+        <v>6</v>
+      </c>
+      <c r="C286">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D286" s="8"/>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A287" s="4">
+        <v>284</v>
+      </c>
+      <c r="B287" s="3">
+        <v>6</v>
+      </c>
+      <c r="C287">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D287" s="9"/>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A288" s="4">
+        <v>285</v>
+      </c>
+      <c r="B288" s="3">
+        <v>6</v>
+      </c>
+      <c r="C288">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D288" s="10"/>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A289" s="4">
+        <v>286</v>
+      </c>
+      <c r="B289" s="3">
+        <v>6</v>
+      </c>
+      <c r="C289">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D289" s="11"/>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A290" s="4">
+        <v>287</v>
+      </c>
+      <c r="B290" s="3">
+        <v>6</v>
+      </c>
+      <c r="C290">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D290" s="12"/>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A291" s="4">
+        <v>288</v>
+      </c>
+      <c r="B291" s="3">
+        <v>6</v>
+      </c>
+      <c r="C291">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D291" s="6"/>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A292" s="4">
+        <v>289</v>
+      </c>
+      <c r="B292" s="3">
+        <v>6</v>
+      </c>
+      <c r="C292">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D292" s="7"/>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A293" s="4">
+        <v>290</v>
+      </c>
+      <c r="B293" s="3">
+        <v>6</v>
+      </c>
+      <c r="C293">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D293" s="8"/>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A294" s="4">
+        <v>291</v>
+      </c>
+      <c r="B294" s="3">
+        <v>6</v>
+      </c>
+      <c r="C294">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D294" s="9"/>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A295" s="4">
+        <v>292</v>
+      </c>
+      <c r="B295" s="3">
+        <v>6</v>
+      </c>
+      <c r="C295">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D295" s="10"/>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A296" s="4">
+        <v>293</v>
+      </c>
+      <c r="B296" s="3">
+        <v>6</v>
+      </c>
+      <c r="C296">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D296" s="11"/>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A297" s="4">
+        <v>294</v>
+      </c>
+      <c r="B297" s="3">
+        <v>6</v>
+      </c>
+      <c r="C297">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D297" s="12"/>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A298" s="4">
+        <v>295</v>
+      </c>
+      <c r="B298" s="3">
+        <v>6</v>
+      </c>
+      <c r="C298">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D298" s="6"/>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A299" s="4">
+        <v>296</v>
+      </c>
+      <c r="B299" s="3">
+        <v>6</v>
+      </c>
+      <c r="C299">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D299" s="7"/>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A300" s="4">
+        <v>297</v>
+      </c>
+      <c r="B300" s="3">
+        <v>6</v>
+      </c>
+      <c r="C300">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D300" s="8"/>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A301" s="4">
+        <v>298</v>
+      </c>
+      <c r="B301" s="3">
+        <v>6</v>
+      </c>
+      <c r="C301">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D301" s="9"/>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A302" s="4">
+        <v>299</v>
+      </c>
+      <c r="B302" s="3">
+        <v>6</v>
+      </c>
+      <c r="C302">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D302" s="10"/>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A303" s="4">
+        <v>300</v>
+      </c>
+      <c r="B303" s="3">
+        <v>6</v>
+      </c>
+      <c r="C303">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D303" s="11"/>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A304" s="4">
+        <v>301</v>
+      </c>
+      <c r="B304" s="3">
+        <v>6</v>
+      </c>
+      <c r="C304">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D304" s="12"/>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A305" s="4">
+        <v>302</v>
+      </c>
+      <c r="B305" s="3">
+        <v>6</v>
+      </c>
+      <c r="C305">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D305" s="6"/>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A306" s="4">
+        <v>303</v>
+      </c>
+      <c r="B306" s="3">
+        <v>6</v>
+      </c>
+      <c r="C306">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D306" s="7"/>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A307" s="4">
+        <v>304</v>
+      </c>
+      <c r="B307" s="3">
+        <v>6</v>
+      </c>
+      <c r="C307">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D307" s="8"/>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A308" s="4">
+        <v>305</v>
+      </c>
+      <c r="B308" s="3">
+        <v>6</v>
+      </c>
+      <c r="C308">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D308" s="9"/>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A309" s="4">
+        <v>306</v>
+      </c>
+      <c r="B309" s="3">
+        <v>6</v>
+      </c>
+      <c r="C309">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D309" s="10"/>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A310" s="4">
+        <v>307</v>
+      </c>
+      <c r="B310" s="3">
+        <v>6</v>
+      </c>
+      <c r="C310">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D310" s="11"/>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A311" s="4">
+        <v>308</v>
+      </c>
+      <c r="B311" s="3">
+        <v>6</v>
+      </c>
+      <c r="C311">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D311" s="12"/>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A312" s="4">
+        <v>309</v>
+      </c>
+      <c r="B312" s="3">
+        <v>6</v>
+      </c>
+      <c r="C312">
+        <v>9.9999999999999006E-2</v>
+      </c>
+      <c r="D312" s="6"/>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A313" s="4">
+        <v>310</v>
+      </c>
+      <c r="B313" s="3">
+        <v>6</v>
+      </c>
+      <c r="C313">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D313" s="7"/>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A314" s="4">
+        <v>311</v>
+      </c>
+      <c r="B314" s="3">
+        <v>6</v>
+      </c>
+      <c r="C314">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D314" s="8"/>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A315" s="4">
+        <v>312</v>
+      </c>
+      <c r="B315" s="3">
+        <v>6</v>
+      </c>
+      <c r="C315">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D315" s="9"/>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A316" s="4">
+        <v>313</v>
+      </c>
+      <c r="B316" s="3">
+        <v>6</v>
+      </c>
+      <c r="C316">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D316" s="10"/>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A317" s="4">
+        <v>314</v>
+      </c>
+      <c r="B317" s="3">
+        <v>6</v>
+      </c>
+      <c r="C317">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D317" s="11"/>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A318" s="4">
+        <v>315</v>
+      </c>
+      <c r="B318" s="3">
+        <v>6</v>
+      </c>
+      <c r="C318">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D318" s="12"/>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A319" s="4">
+        <v>316</v>
+      </c>
+      <c r="B319" s="3">
+        <v>6</v>
+      </c>
+      <c r="C319">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D319" s="6"/>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A320" s="4">
+        <v>317</v>
+      </c>
+      <c r="B320" s="3">
+        <v>6</v>
+      </c>
+      <c r="C320">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D320" s="7"/>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A321" s="4">
+        <v>318</v>
+      </c>
+      <c r="B321" s="3">
+        <v>6</v>
+      </c>
+      <c r="C321">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D321" s="8"/>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A322" s="4">
+        <v>319</v>
+      </c>
+      <c r="B322" s="3">
+        <v>6</v>
+      </c>
+      <c r="C322">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D322" s="9"/>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A323" s="4">
+        <v>320</v>
+      </c>
+      <c r="B323" s="3">
+        <v>6</v>
+      </c>
+      <c r="C323">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D323" s="10"/>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A324" s="4">
+        <v>321</v>
+      </c>
+      <c r="B324" s="3">
+        <v>6</v>
+      </c>
+      <c r="C324">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D324" s="11"/>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A325" s="4">
+        <v>322</v>
+      </c>
+      <c r="B325" s="3">
+        <v>6</v>
+      </c>
+      <c r="C325">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D325" s="12"/>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A326" s="4">
+        <v>323</v>
+      </c>
+      <c r="B326" s="3">
+        <v>6</v>
+      </c>
+      <c r="C326">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D326" s="6"/>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A327" s="4">
+        <v>324</v>
+      </c>
+      <c r="B327" s="3">
+        <v>6</v>
+      </c>
+      <c r="C327">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D327" s="7"/>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A328" s="4">
+        <v>325</v>
+      </c>
+      <c r="B328" s="3">
+        <v>6</v>
+      </c>
+      <c r="C328">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D328" s="8"/>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A329" s="4">
+        <v>326</v>
+      </c>
+      <c r="B329" s="3">
+        <v>6</v>
+      </c>
+      <c r="C329">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D329" s="9"/>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A330" s="4">
+        <v>327</v>
+      </c>
+      <c r="B330" s="3">
+        <v>6</v>
+      </c>
+      <c r="C330">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D330" s="10"/>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A331" s="4">
+        <v>328</v>
+      </c>
+      <c r="B331" s="3">
+        <v>6</v>
+      </c>
+      <c r="C331">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D331" s="11"/>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A332" s="4">
+        <v>329</v>
+      </c>
+      <c r="B332" s="3">
+        <v>6</v>
+      </c>
+      <c r="C332">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D332" s="12"/>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A333" s="4">
+        <v>330</v>
+      </c>
+      <c r="B333" s="3">
+        <v>6</v>
+      </c>
+      <c r="C333">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D333" s="6"/>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A334" s="4">
+        <v>331</v>
+      </c>
+      <c r="B334" s="3">
+        <v>6</v>
+      </c>
+      <c r="C334">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D334" s="7"/>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A335" s="4">
+        <v>332</v>
+      </c>
+      <c r="B335" s="3">
+        <v>6</v>
+      </c>
+      <c r="C335">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D335" s="8"/>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A336" s="4">
+        <v>333</v>
+      </c>
+      <c r="B336" s="3">
+        <v>6</v>
+      </c>
+      <c r="C336">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D336" s="9"/>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A337" s="4">
+        <v>334</v>
+      </c>
+      <c r="B337" s="3">
+        <v>6</v>
+      </c>
+      <c r="C337">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D337" s="10"/>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A338" s="4">
+        <v>335</v>
+      </c>
+      <c r="B338" s="3">
+        <v>6</v>
+      </c>
+      <c r="C338">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D338" s="11"/>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A339" s="4">
+        <v>336</v>
+      </c>
+      <c r="B339" s="3">
+        <v>6</v>
+      </c>
+      <c r="C339">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D339" s="12"/>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A340" s="4">
+        <v>337</v>
+      </c>
+      <c r="B340" s="3">
+        <v>6</v>
+      </c>
+      <c r="C340">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D340" s="6"/>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A341" s="4">
+        <v>338</v>
+      </c>
+      <c r="B341" s="3">
+        <v>6</v>
+      </c>
+      <c r="C341">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D341" s="7"/>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A342" s="4">
+        <v>339</v>
+      </c>
+      <c r="B342" s="3">
+        <v>6</v>
+      </c>
+      <c r="C342">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D342" s="8"/>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A343" s="4">
+        <v>340</v>
+      </c>
+      <c r="B343" s="3">
+        <v>6</v>
+      </c>
+      <c r="C343">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D343" s="9"/>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A344" s="4">
+        <v>341</v>
+      </c>
+      <c r="B344" s="3">
+        <v>6</v>
+      </c>
+      <c r="C344">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D344" s="10"/>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A345" s="4">
+        <v>342</v>
+      </c>
+      <c r="B345" s="3">
+        <v>6</v>
+      </c>
+      <c r="C345">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D345" s="11"/>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A346" s="4">
+        <v>343</v>
+      </c>
+      <c r="B346" s="3">
+        <v>6</v>
+      </c>
+      <c r="C346">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D346" s="12"/>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A347" s="4">
+        <v>344</v>
+      </c>
+      <c r="B347" s="3">
+        <v>6</v>
+      </c>
+      <c r="C347">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D347" s="6"/>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A348" s="4">
+        <v>345</v>
+      </c>
+      <c r="B348" s="3">
+        <v>6</v>
+      </c>
+      <c r="C348">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D348" s="7"/>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A349" s="4">
+        <v>346</v>
+      </c>
+      <c r="B349" s="3">
+        <v>6</v>
+      </c>
+      <c r="C349">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D349" s="8"/>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A350" s="4">
+        <v>347</v>
+      </c>
+      <c r="B350" s="3">
+        <v>6</v>
+      </c>
+      <c r="C350">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D350" s="9"/>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A351" s="4">
+        <v>348</v>
+      </c>
+      <c r="B351" s="3">
+        <v>6</v>
+      </c>
+      <c r="C351">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D351" s="10"/>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A352" s="4">
+        <v>349</v>
+      </c>
+      <c r="B352" s="3">
+        <v>6</v>
+      </c>
+      <c r="C352">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D352" s="11"/>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A353" s="4">
+        <v>350</v>
+      </c>
+      <c r="B353" s="3">
+        <v>6</v>
+      </c>
+      <c r="C353">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D353" s="12"/>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A354" s="4">
+        <v>351</v>
+      </c>
+      <c r="B354" s="3">
+        <v>6</v>
+      </c>
+      <c r="C354">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D354" s="6"/>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A355" s="4">
+        <v>352</v>
+      </c>
+      <c r="B355" s="3">
+        <v>6</v>
+      </c>
+      <c r="C355">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D355" s="7"/>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A356" s="4">
+        <v>353</v>
+      </c>
+      <c r="B356" s="3">
+        <v>6</v>
+      </c>
+      <c r="C356">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D356" s="8"/>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A357" s="4">
+        <v>354</v>
+      </c>
+      <c r="B357" s="3">
+        <v>6</v>
+      </c>
+      <c r="C357">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D357" s="9"/>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A358" s="4">
+        <v>355</v>
+      </c>
+      <c r="B358" s="3">
+        <v>6</v>
+      </c>
+      <c r="C358">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D358" s="10"/>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A359" s="4">
+        <v>356</v>
+      </c>
+      <c r="B359" s="3">
+        <v>6</v>
+      </c>
+      <c r="C359">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D359" s="11"/>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A360" s="4">
+        <v>357</v>
+      </c>
+      <c r="B360" s="3">
+        <v>6</v>
+      </c>
+      <c r="C360">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D360" s="12"/>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A361" s="4">
+        <v>358</v>
+      </c>
+      <c r="B361" s="3">
+        <v>6</v>
+      </c>
+      <c r="C361">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D361" s="6"/>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A362" s="4">
+        <v>359</v>
+      </c>
+      <c r="B362" s="3">
+        <v>6</v>
+      </c>
+      <c r="C362">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D362" s="7"/>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A363" s="4">
+        <v>360</v>
+      </c>
+      <c r="B363" s="3">
+        <v>6</v>
+      </c>
+      <c r="C363">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D363" s="8"/>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A364" s="4">
+        <v>361</v>
+      </c>
+      <c r="B364" s="3">
+        <v>6</v>
+      </c>
+      <c r="C364">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D364" s="9"/>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A365" s="4">
+        <v>362</v>
+      </c>
+      <c r="B365" s="3">
+        <v>6</v>
+      </c>
+      <c r="C365">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D365" s="10"/>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A366" s="4">
+        <v>363</v>
+      </c>
+      <c r="B366" s="3">
+        <v>6</v>
+      </c>
+      <c r="C366">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D366" s="11"/>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A367" s="4">
+        <v>364</v>
+      </c>
+      <c r="B367" s="3">
+        <v>6</v>
+      </c>
+      <c r="C367">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D367" s="12"/>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A368" s="4">
+        <v>365</v>
+      </c>
+      <c r="B368" s="3">
+        <v>6</v>
+      </c>
+      <c r="C368">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D368" s="6"/>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A369" s="4">
+        <v>366</v>
+      </c>
+      <c r="B369" s="3">
+        <v>6</v>
+      </c>
+      <c r="C369">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D369" s="7"/>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A370" s="4">
+        <v>367</v>
+      </c>
+      <c r="B370" s="3">
+        <v>6</v>
+      </c>
+      <c r="C370">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D370" s="8"/>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A371" s="4">
+        <v>368</v>
+      </c>
+      <c r="B371" s="3">
+        <v>6</v>
+      </c>
+      <c r="C371">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D371" s="9"/>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A372" s="4">
+        <v>369</v>
+      </c>
+      <c r="B372" s="3">
+        <v>6</v>
+      </c>
+      <c r="C372">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D372" s="10"/>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A373" s="4">
+        <v>370</v>
+      </c>
+      <c r="B373" s="3">
+        <v>6</v>
+      </c>
+      <c r="C373">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D373" s="11"/>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A374" s="4">
+        <v>371</v>
+      </c>
+      <c r="B374" s="3">
+        <v>6</v>
+      </c>
+      <c r="C374">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D374" s="12"/>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A375" s="4">
+        <v>372</v>
+      </c>
+      <c r="B375" s="3">
+        <v>6</v>
+      </c>
+      <c r="C375">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D375" s="6"/>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A376" s="4">
+        <v>373</v>
+      </c>
+      <c r="B376" s="3">
+        <v>6</v>
+      </c>
+      <c r="C376">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D376" s="7"/>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A377" s="4">
+        <v>374</v>
+      </c>
+      <c r="B377" s="3">
+        <v>6</v>
+      </c>
+      <c r="C377">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D377" s="8"/>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A378" s="4">
+        <v>375</v>
+      </c>
+      <c r="B378" s="3">
+        <v>6</v>
+      </c>
+      <c r="C378">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D378" s="9"/>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A379" s="4">
+        <v>376</v>
+      </c>
+      <c r="B379" s="3">
+        <v>6</v>
+      </c>
+      <c r="C379">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D379" s="10"/>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A380" s="4">
+        <v>377</v>
+      </c>
+      <c r="B380" s="3">
+        <v>6</v>
+      </c>
+      <c r="C380">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D380" s="11"/>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A381" s="4">
+        <v>378</v>
+      </c>
+      <c r="B381" s="3">
+        <v>6</v>
+      </c>
+      <c r="C381">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D381" s="12"/>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A382" s="4">
+        <v>379</v>
+      </c>
+      <c r="B382" s="3">
+        <v>6</v>
+      </c>
+      <c r="C382">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D382" s="6"/>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A383" s="4">
+        <v>380</v>
+      </c>
+      <c r="B383" s="3">
+        <v>6</v>
+      </c>
+      <c r="C383">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D383" s="7"/>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A384" s="4">
+        <v>381</v>
+      </c>
+      <c r="B384" s="3">
+        <v>6</v>
+      </c>
+      <c r="C384">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D384" s="8"/>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A385" s="4">
+        <v>382</v>
+      </c>
+      <c r="B385" s="3">
+        <v>6</v>
+      </c>
+      <c r="C385">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D385" s="9"/>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A386" s="4">
+        <v>383</v>
+      </c>
+      <c r="B386" s="3">
+        <v>6</v>
+      </c>
+      <c r="C386">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D386" s="10"/>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A387" s="4">
+        <v>384</v>
+      </c>
+      <c r="B387" s="3">
+        <v>6</v>
+      </c>
+      <c r="C387">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D387" s="11"/>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A388" s="4">
+        <v>385</v>
+      </c>
+      <c r="B388" s="3">
+        <v>6</v>
+      </c>
+      <c r="C388">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D388" s="12"/>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A389" s="4">
+        <v>386</v>
+      </c>
+      <c r="B389" s="3">
+        <v>6</v>
+      </c>
+      <c r="C389">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D389" s="6"/>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A390" s="4">
+        <v>387</v>
+      </c>
+      <c r="B390" s="3">
+        <v>6</v>
+      </c>
+      <c r="C390">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D390" s="7"/>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A391" s="4">
+        <v>388</v>
+      </c>
+      <c r="B391" s="3">
+        <v>6</v>
+      </c>
+      <c r="C391">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D391" s="8"/>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A392" s="4">
+        <v>389</v>
+      </c>
+      <c r="B392" s="3">
+        <v>6</v>
+      </c>
+      <c r="C392">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D392" s="9"/>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A393" s="4">
+        <v>390</v>
+      </c>
+      <c r="B393" s="3">
+        <v>6</v>
+      </c>
+      <c r="C393">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D393" s="6"/>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A394" s="4">
+        <v>391</v>
+      </c>
+      <c r="B394" s="3">
+        <v>6</v>
+      </c>
+      <c r="C394">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D394" s="7"/>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A395" s="4">
+        <v>392</v>
+      </c>
+      <c r="B395" s="3">
+        <v>6</v>
+      </c>
+      <c r="C395">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D395" s="8"/>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A396" s="4">
+        <v>393</v>
+      </c>
+      <c r="B396" s="3">
+        <v>6</v>
+      </c>
+      <c r="C396">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D396" s="9"/>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A397" s="4">
+        <v>394</v>
+      </c>
+      <c r="B397" s="3">
+        <v>6</v>
+      </c>
+      <c r="C397">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D397" s="10"/>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A398" s="4">
+        <v>395</v>
+      </c>
+      <c r="B398" s="3">
+        <v>6</v>
+      </c>
+      <c r="C398">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D398" s="11"/>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A399" s="4">
+        <v>396</v>
+      </c>
+      <c r="B399" s="3">
+        <v>6</v>
+      </c>
+      <c r="C399">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D399" s="12"/>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A400" s="4">
+        <v>397</v>
+      </c>
+      <c r="B400" s="3">
+        <v>6</v>
+      </c>
+      <c r="C400">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D400" s="6"/>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A401" s="4">
+        <v>398</v>
+      </c>
+      <c r="B401" s="3">
+        <v>6</v>
+      </c>
+      <c r="C401">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D401" s="7"/>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A402" s="4">
+        <v>399</v>
+      </c>
+      <c r="B402" s="3">
+        <v>6</v>
+      </c>
+      <c r="C402">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D402" s="8"/>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A403" s="4">
+        <v>400</v>
+      </c>
+      <c r="B403" s="3">
+        <v>6</v>
+      </c>
+      <c r="C403">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D403" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2926,7 +5326,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FBBFF61-F2A9-4270-86EF-F5F8D76F72F6}">
-  <dimension ref="A1:B207"/>
+  <dimension ref="A1:B403"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -4558,20 +6958,1604 @@
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A204" s="4"/>
-      <c r="B204" s="5"/>
+      <c r="A204" s="4">
+        <v>201</v>
+      </c>
+      <c r="B204" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A205" s="4"/>
-      <c r="B205" s="5"/>
+      <c r="A205" s="4">
+        <v>202</v>
+      </c>
+      <c r="B205" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A206" s="4"/>
-      <c r="B206" s="5"/>
+      <c r="A206" s="4">
+        <v>203</v>
+      </c>
+      <c r="B206" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A207" s="4"/>
-      <c r="B207" s="5"/>
+      <c r="A207" s="4">
+        <v>204</v>
+      </c>
+      <c r="B207" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" s="4">
+        <v>205</v>
+      </c>
+      <c r="B208" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" s="4">
+        <v>206</v>
+      </c>
+      <c r="B209" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" s="4">
+        <v>207</v>
+      </c>
+      <c r="B210" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" s="4">
+        <v>208</v>
+      </c>
+      <c r="B211" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212" s="4">
+        <v>209</v>
+      </c>
+      <c r="B212" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213" s="4">
+        <v>210</v>
+      </c>
+      <c r="B213" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214" s="4">
+        <v>211</v>
+      </c>
+      <c r="B214" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215" s="4">
+        <v>212</v>
+      </c>
+      <c r="B215" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216" s="4">
+        <v>213</v>
+      </c>
+      <c r="B216" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217" s="4">
+        <v>214</v>
+      </c>
+      <c r="B217" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218" s="4">
+        <v>215</v>
+      </c>
+      <c r="B218" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219" s="4">
+        <v>216</v>
+      </c>
+      <c r="B219" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220" s="4">
+        <v>217</v>
+      </c>
+      <c r="B220" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221" s="4">
+        <v>218</v>
+      </c>
+      <c r="B221" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222" s="4">
+        <v>219</v>
+      </c>
+      <c r="B222" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223" s="4">
+        <v>220</v>
+      </c>
+      <c r="B223" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224" s="4">
+        <v>221</v>
+      </c>
+      <c r="B224" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225" s="4">
+        <v>222</v>
+      </c>
+      <c r="B225" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226" s="4">
+        <v>223</v>
+      </c>
+      <c r="B226" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227" s="4">
+        <v>224</v>
+      </c>
+      <c r="B227" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228" s="4">
+        <v>225</v>
+      </c>
+      <c r="B228" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229" s="4">
+        <v>226</v>
+      </c>
+      <c r="B229" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230" s="4">
+        <v>227</v>
+      </c>
+      <c r="B230" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231" s="4">
+        <v>228</v>
+      </c>
+      <c r="B231" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232" s="4">
+        <v>229</v>
+      </c>
+      <c r="B232" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233" s="4">
+        <v>230</v>
+      </c>
+      <c r="B233" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234" s="4">
+        <v>231</v>
+      </c>
+      <c r="B234" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235" s="4">
+        <v>232</v>
+      </c>
+      <c r="B235" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236" s="4">
+        <v>233</v>
+      </c>
+      <c r="B236" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237" s="4">
+        <v>234</v>
+      </c>
+      <c r="B237" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238" s="4">
+        <v>235</v>
+      </c>
+      <c r="B238" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239" s="4">
+        <v>236</v>
+      </c>
+      <c r="B239" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240" s="4">
+        <v>237</v>
+      </c>
+      <c r="B240" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241" s="4">
+        <v>238</v>
+      </c>
+      <c r="B241" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242" s="4">
+        <v>239</v>
+      </c>
+      <c r="B242" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243" s="4">
+        <v>240</v>
+      </c>
+      <c r="B243" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244" s="4">
+        <v>241</v>
+      </c>
+      <c r="B244" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245" s="4">
+        <v>242</v>
+      </c>
+      <c r="B245" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246" s="4">
+        <v>243</v>
+      </c>
+      <c r="B246" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247" s="4">
+        <v>244</v>
+      </c>
+      <c r="B247" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248" s="4">
+        <v>245</v>
+      </c>
+      <c r="B248" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249" s="4">
+        <v>246</v>
+      </c>
+      <c r="B249" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250" s="4">
+        <v>247</v>
+      </c>
+      <c r="B250" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251" s="4">
+        <v>248</v>
+      </c>
+      <c r="B251" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252" s="4">
+        <v>249</v>
+      </c>
+      <c r="B252" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253" s="4">
+        <v>250</v>
+      </c>
+      <c r="B253" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254" s="4">
+        <v>251</v>
+      </c>
+      <c r="B254" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255" s="4">
+        <v>252</v>
+      </c>
+      <c r="B255" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256" s="4">
+        <v>253</v>
+      </c>
+      <c r="B256" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257" s="4">
+        <v>254</v>
+      </c>
+      <c r="B257" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258" s="4">
+        <v>255</v>
+      </c>
+      <c r="B258" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259" s="4">
+        <v>256</v>
+      </c>
+      <c r="B259" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260" s="4">
+        <v>257</v>
+      </c>
+      <c r="B260" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261" s="4">
+        <v>258</v>
+      </c>
+      <c r="B261" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262" s="4">
+        <v>259</v>
+      </c>
+      <c r="B262" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263" s="4">
+        <v>260</v>
+      </c>
+      <c r="B263" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264" s="4">
+        <v>261</v>
+      </c>
+      <c r="B264" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A265" s="4">
+        <v>262</v>
+      </c>
+      <c r="B265" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A266" s="4">
+        <v>263</v>
+      </c>
+      <c r="B266" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A267" s="4">
+        <v>264</v>
+      </c>
+      <c r="B267" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A268" s="4">
+        <v>265</v>
+      </c>
+      <c r="B268" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A269" s="4">
+        <v>266</v>
+      </c>
+      <c r="B269" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A270" s="4">
+        <v>267</v>
+      </c>
+      <c r="B270" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A271" s="4">
+        <v>268</v>
+      </c>
+      <c r="B271" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A272" s="4">
+        <v>269</v>
+      </c>
+      <c r="B272" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A273" s="4">
+        <v>270</v>
+      </c>
+      <c r="B273" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A274" s="4">
+        <v>271</v>
+      </c>
+      <c r="B274" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A275" s="4">
+        <v>272</v>
+      </c>
+      <c r="B275" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A276" s="4">
+        <v>273</v>
+      </c>
+      <c r="B276" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A277" s="4">
+        <v>274</v>
+      </c>
+      <c r="B277" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A278" s="4">
+        <v>275</v>
+      </c>
+      <c r="B278" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A279" s="4">
+        <v>276</v>
+      </c>
+      <c r="B279" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A280" s="4">
+        <v>277</v>
+      </c>
+      <c r="B280" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A281" s="4">
+        <v>278</v>
+      </c>
+      <c r="B281" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A282" s="4">
+        <v>279</v>
+      </c>
+      <c r="B282" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A283" s="4">
+        <v>280</v>
+      </c>
+      <c r="B283" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A284" s="4">
+        <v>281</v>
+      </c>
+      <c r="B284" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A285" s="4">
+        <v>282</v>
+      </c>
+      <c r="B285" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A286" s="4">
+        <v>283</v>
+      </c>
+      <c r="B286" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A287" s="4">
+        <v>284</v>
+      </c>
+      <c r="B287" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A288" s="4">
+        <v>285</v>
+      </c>
+      <c r="B288" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A289" s="4">
+        <v>286</v>
+      </c>
+      <c r="B289" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A290" s="4">
+        <v>287</v>
+      </c>
+      <c r="B290" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A291" s="4">
+        <v>288</v>
+      </c>
+      <c r="B291" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A292" s="4">
+        <v>289</v>
+      </c>
+      <c r="B292" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A293" s="4">
+        <v>290</v>
+      </c>
+      <c r="B293" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A294" s="4">
+        <v>291</v>
+      </c>
+      <c r="B294" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A295" s="4">
+        <v>292</v>
+      </c>
+      <c r="B295" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A296" s="4">
+        <v>293</v>
+      </c>
+      <c r="B296" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A297" s="4">
+        <v>294</v>
+      </c>
+      <c r="B297" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A298" s="4">
+        <v>295</v>
+      </c>
+      <c r="B298" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A299" s="4">
+        <v>296</v>
+      </c>
+      <c r="B299" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A300" s="4">
+        <v>297</v>
+      </c>
+      <c r="B300" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A301" s="4">
+        <v>298</v>
+      </c>
+      <c r="B301" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A302" s="4">
+        <v>299</v>
+      </c>
+      <c r="B302" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A303" s="4">
+        <v>300</v>
+      </c>
+      <c r="B303" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A304" s="4">
+        <v>301</v>
+      </c>
+      <c r="B304" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A305" s="4">
+        <v>302</v>
+      </c>
+      <c r="B305" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A306" s="4">
+        <v>303</v>
+      </c>
+      <c r="B306" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A307" s="4">
+        <v>304</v>
+      </c>
+      <c r="B307" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A308" s="4">
+        <v>305</v>
+      </c>
+      <c r="B308" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A309" s="4">
+        <v>306</v>
+      </c>
+      <c r="B309" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A310" s="4">
+        <v>307</v>
+      </c>
+      <c r="B310" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A311" s="4">
+        <v>308</v>
+      </c>
+      <c r="B311" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A312" s="4">
+        <v>309</v>
+      </c>
+      <c r="B312" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A313" s="4">
+        <v>310</v>
+      </c>
+      <c r="B313" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A314" s="4">
+        <v>311</v>
+      </c>
+      <c r="B314" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A315" s="4">
+        <v>312</v>
+      </c>
+      <c r="B315" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A316" s="4">
+        <v>313</v>
+      </c>
+      <c r="B316" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A317" s="4">
+        <v>314</v>
+      </c>
+      <c r="B317" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A318" s="4">
+        <v>315</v>
+      </c>
+      <c r="B318" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A319" s="4">
+        <v>316</v>
+      </c>
+      <c r="B319" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A320" s="4">
+        <v>317</v>
+      </c>
+      <c r="B320" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A321" s="4">
+        <v>318</v>
+      </c>
+      <c r="B321" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A322" s="4">
+        <v>319</v>
+      </c>
+      <c r="B322" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A323" s="4">
+        <v>320</v>
+      </c>
+      <c r="B323" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A324" s="4">
+        <v>321</v>
+      </c>
+      <c r="B324" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A325" s="4">
+        <v>322</v>
+      </c>
+      <c r="B325" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A326" s="4">
+        <v>323</v>
+      </c>
+      <c r="B326" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A327" s="4">
+        <v>324</v>
+      </c>
+      <c r="B327" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A328" s="4">
+        <v>325</v>
+      </c>
+      <c r="B328" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A329" s="4">
+        <v>326</v>
+      </c>
+      <c r="B329" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A330" s="4">
+        <v>327</v>
+      </c>
+      <c r="B330" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A331" s="4">
+        <v>328</v>
+      </c>
+      <c r="B331" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A332" s="4">
+        <v>329</v>
+      </c>
+      <c r="B332" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A333" s="4">
+        <v>330</v>
+      </c>
+      <c r="B333" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A334" s="4">
+        <v>331</v>
+      </c>
+      <c r="B334" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A335" s="4">
+        <v>332</v>
+      </c>
+      <c r="B335" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A336" s="4">
+        <v>333</v>
+      </c>
+      <c r="B336" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A337" s="4">
+        <v>334</v>
+      </c>
+      <c r="B337" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A338" s="4">
+        <v>335</v>
+      </c>
+      <c r="B338" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A339" s="4">
+        <v>336</v>
+      </c>
+      <c r="B339" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A340" s="4">
+        <v>337</v>
+      </c>
+      <c r="B340" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A341" s="4">
+        <v>338</v>
+      </c>
+      <c r="B341" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A342" s="4">
+        <v>339</v>
+      </c>
+      <c r="B342" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A343" s="4">
+        <v>340</v>
+      </c>
+      <c r="B343" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A344" s="4">
+        <v>341</v>
+      </c>
+      <c r="B344" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A345" s="4">
+        <v>342</v>
+      </c>
+      <c r="B345" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A346" s="4">
+        <v>343</v>
+      </c>
+      <c r="B346" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A347" s="4">
+        <v>344</v>
+      </c>
+      <c r="B347" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A348" s="4">
+        <v>345</v>
+      </c>
+      <c r="B348" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A349" s="4">
+        <v>346</v>
+      </c>
+      <c r="B349" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A350" s="4">
+        <v>347</v>
+      </c>
+      <c r="B350" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A351" s="4">
+        <v>348</v>
+      </c>
+      <c r="B351" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A352" s="4">
+        <v>349</v>
+      </c>
+      <c r="B352" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A353" s="4">
+        <v>350</v>
+      </c>
+      <c r="B353" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A354" s="4">
+        <v>351</v>
+      </c>
+      <c r="B354" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A355" s="4">
+        <v>352</v>
+      </c>
+      <c r="B355" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A356" s="4">
+        <v>353</v>
+      </c>
+      <c r="B356" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A357" s="4">
+        <v>354</v>
+      </c>
+      <c r="B357" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A358" s="4">
+        <v>355</v>
+      </c>
+      <c r="B358" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A359" s="4">
+        <v>356</v>
+      </c>
+      <c r="B359" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A360" s="4">
+        <v>357</v>
+      </c>
+      <c r="B360" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A361" s="4">
+        <v>358</v>
+      </c>
+      <c r="B361" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A362" s="4">
+        <v>359</v>
+      </c>
+      <c r="B362" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A363" s="4">
+        <v>360</v>
+      </c>
+      <c r="B363" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A364" s="4">
+        <v>361</v>
+      </c>
+      <c r="B364" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A365" s="4">
+        <v>362</v>
+      </c>
+      <c r="B365" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A366" s="4">
+        <v>363</v>
+      </c>
+      <c r="B366" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A367" s="4">
+        <v>364</v>
+      </c>
+      <c r="B367" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A368" s="4">
+        <v>365</v>
+      </c>
+      <c r="B368" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A369" s="4">
+        <v>366</v>
+      </c>
+      <c r="B369" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A370" s="4">
+        <v>367</v>
+      </c>
+      <c r="B370" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A371" s="4">
+        <v>368</v>
+      </c>
+      <c r="B371" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A372" s="4">
+        <v>369</v>
+      </c>
+      <c r="B372" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A373" s="4">
+        <v>370</v>
+      </c>
+      <c r="B373" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A374" s="4">
+        <v>371</v>
+      </c>
+      <c r="B374" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A375" s="4">
+        <v>372</v>
+      </c>
+      <c r="B375" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A376" s="4">
+        <v>373</v>
+      </c>
+      <c r="B376" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A377" s="4">
+        <v>374</v>
+      </c>
+      <c r="B377" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A378" s="4">
+        <v>375</v>
+      </c>
+      <c r="B378" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A379" s="4">
+        <v>376</v>
+      </c>
+      <c r="B379" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A380" s="4">
+        <v>377</v>
+      </c>
+      <c r="B380" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A381" s="4">
+        <v>378</v>
+      </c>
+      <c r="B381" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A382" s="4">
+        <v>379</v>
+      </c>
+      <c r="B382" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A383" s="4">
+        <v>380</v>
+      </c>
+      <c r="B383" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A384" s="4">
+        <v>381</v>
+      </c>
+      <c r="B384" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A385" s="4">
+        <v>382</v>
+      </c>
+      <c r="B385" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A386" s="4">
+        <v>383</v>
+      </c>
+      <c r="B386" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A387" s="4">
+        <v>384</v>
+      </c>
+      <c r="B387" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A388" s="4">
+        <v>385</v>
+      </c>
+      <c r="B388" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A389" s="4">
+        <v>386</v>
+      </c>
+      <c r="B389" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A390" s="4">
+        <v>387</v>
+      </c>
+      <c r="B390" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A391" s="4">
+        <v>388</v>
+      </c>
+      <c r="B391" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A392" s="4">
+        <v>389</v>
+      </c>
+      <c r="B392" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A393" s="4">
+        <v>390</v>
+      </c>
+      <c r="B393" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A394" s="4">
+        <v>391</v>
+      </c>
+      <c r="B394" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A395" s="4">
+        <v>392</v>
+      </c>
+      <c r="B395" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A396" s="4">
+        <v>393</v>
+      </c>
+      <c r="B396" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A397" s="4">
+        <v>394</v>
+      </c>
+      <c r="B397" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A398" s="4">
+        <v>395</v>
+      </c>
+      <c r="B398" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A399" s="4">
+        <v>396</v>
+      </c>
+      <c r="B399" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A400" s="4">
+        <v>397</v>
+      </c>
+      <c r="B400" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A401" s="4">
+        <v>398</v>
+      </c>
+      <c r="B401" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A402" s="4">
+        <v>399</v>
+      </c>
+      <c r="B402" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A403" s="4">
+        <v>400</v>
+      </c>
+      <c r="B403" s="5">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
